--- a/CBT_2026_2회/산업안전기사_2026_2회_문항등록.xlsx
+++ b/CBT_2026_2회/산업안전기사_2026_2회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AH3" s="32" t="inlineStr">
         <is>
-          <t>① 2.5G 4/10 은 녹색으로 안내표지에 쓴다.&lt;br&gt;② 5Y 8.5/12 는 노란색으로 경고표지에 쓴다.&lt;br&gt;④ 7.5R 4/14 는 빨간색으로 금지·경고표지에 쓴다.</t>
+          <t>① 2.5G 4/10은 녹색으로 안내표지에 쓴다.&lt;br&gt;② 5Y 8.5/12는 노란색으로 경고표지에 쓴다.&lt;br&gt;④ 7.5R 4/14는 빨간색으로 금지·경고표지에 쓴다.</t>
         </is>
       </c>
       <c r="AI3" s="32" t="inlineStr">
@@ -1674,7 +1674,11 @@
           <t>산업안전보건법령상 협의체 구성 및 운영에 관한 사항으로 ( )에 알맞은 내용은?</t>
         </is>
       </c>
-      <c r="V5" s="32" t="inlineStr"/>
+      <c r="V5" s="32" t="inlineStr">
+        <is>
+          <t>도급인은 관계수급인 근로자가 도급인의 사업장에서 작업을 하는 경우 도급인과 수급인을 구성원으로 하는 안전 및 보건에 관한 협의체를 구성 및 운영하여야 한다. 이 협의체는 (      ) 정기적으로 회의를 개최하고 그 결과를 기록·보존해야 한다.</t>
+        </is>
+      </c>
       <c r="W5" s="32" t="inlineStr"/>
       <c r="X5" s="32" t="inlineStr">
         <is>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="AH8" s="32" t="inlineStr">
         <is>
-          <t>① 16 [%] 는 이미 산소결핍 상태다.&lt;br&gt;③ 21 [%] 는 정상 공기의 산소농도로, 최소기준이 아니다.&lt;br&gt;④ 23.5 [%] 는 적정공기의 상한이다.</t>
+          <t>① 16 [%]는 이미 산소결핍 상태다.&lt;br&gt;③ 21 [%]는 정상 공기의 산소농도로, 최소기준이 아니다.&lt;br&gt;④ 23.5 [%]는 적정공기의 상한이다.</t>
         </is>
       </c>
       <c r="AI8" s="32" t="inlineStr">
@@ -2355,7 +2359,7 @@
       </c>
       <c r="AH10" s="32" t="inlineStr">
         <is>
-          <t>① 안정기와 불안정기가 바뀌는 교차점을 위험일이라 한다.&lt;br&gt;③ 지성적 리듬은 I 로 표시하며 사고력과 관련된다.&lt;br&gt;④ 육체적 리듬은 식욕·활동력과 관련된다.</t>
+          <t>① 안정기와 불안정기가 바뀌는 교차점을 위험일이라 한다.&lt;br&gt;③ 지성적 리듬은 I로 표시하며 사고력과 관련된다.&lt;br&gt;④ 육체적 리듬은 식욕·활동력과 관련된다.</t>
         </is>
       </c>
       <c r="AI10" s="32" t="inlineStr">
@@ -2742,12 +2746,12 @@
       </c>
       <c r="AH13" s="32" t="inlineStr">
         <is>
-          <t>② ATT 는 대상에 제한이 없는 과정이다.&lt;br&gt;③ MTP 는 중간관리자를 대상으로 한다.&lt;br&gt;④ ATP 는 최고경영자를 대상으로 한다.</t>
+          <t>② ATT는 대상에 제한이 없는 과정이다.&lt;br&gt;③ MTP는 중간관리자를 대상으로 한다.&lt;br&gt;④ ATP는 최고경영자를 대상으로 한다.</t>
         </is>
       </c>
       <c r="AI13" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;기업 내 정형교육&lt;/strong&gt;&lt;br&gt;TWI 의 JST 에서 S 는 &lt;strong&gt;Safety&lt;/strong&gt;다. Standardization 으로 바꿔 놓는 함정이 자주 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; TWI 네 과정 — 「&lt;u&gt;방 · 인 · 지 · 안&lt;/u&gt;」.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;기업 내 정형교육&lt;/strong&gt;&lt;br&gt;TWI의 JST에서 S는 &lt;strong&gt;Safety&lt;/strong&gt;다. Standardization으로 바꿔 놓는 함정이 자주 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; TWI 네 과정 — 「&lt;u&gt;방 · 인 · 지 · 안&lt;/u&gt;」.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="Q18" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" s="32" t="inlineStr">
         <is>
@@ -3339,7 +3343,7 @@
       <c r="S18" s="32" t="inlineStr"/>
       <c r="T18" s="32" t="inlineStr">
         <is>
-          <t>원본 시행일 2022.03.05 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도1</t>
+          <t>원본 시행일 2022.03.05 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2</t>
         </is>
       </c>
       <c r="U18" s="32" t="inlineStr">
@@ -3347,7 +3351,11 @@
           <t>안전점검을 점검시기에 따라 구분할 때 다음에서 설명하는 안전점검은?</t>
         </is>
       </c>
-      <c r="V18" s="32" t="inlineStr"/>
+      <c r="V18" s="32" t="inlineStr">
+        <is>
+          <t>작업담당자 또는 해당 관리감독자가 맡고 있는 공정의 설비, 기계, 공구 등을 매일 작업 전 또는 작업 중에 일상적으로 실시하는 안전점검</t>
+        </is>
+      </c>
       <c r="W18" s="32" t="inlineStr"/>
       <c r="X18" s="32" t="inlineStr">
         <is>
@@ -3517,7 +3525,7 @@
       </c>
       <c r="AI19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;재해의 직접원인과 간접원인&lt;/strong&gt;&lt;br&gt;하인리히는 직접원인 가운데 &lt;strong&gt;불안전한 행동 88 [%]&lt;/strong&gt;, 불안전한 상태 10 [%], 불가항력 2 [%] 로 보았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직접원인은 「행동」과 「상태」 둘뿐&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;재해의 직접원인과 간접원인&lt;/strong&gt;&lt;br&gt;하인리히는 직접원인 가운데 &lt;strong&gt;불안전한 행동 88 [%]&lt;/strong&gt;, 불안전한 상태 10 [%], 불가항력 2 [%]로 보았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직접원인은 「행동」과 「상태」 둘뿐&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3773,7 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>현장을 정리하면 &lt;strong&gt;증거가 사라진다&lt;/strong&gt;. 재해조사는 &lt;strong&gt;현장이 보존된 상태에서 되도록 빨리&lt;/strong&gt; 해야 한다.</t>
+          <t>현장을 정리하면 &lt;strong&gt;증거가 사라진다&lt;/strong&gt;. 재해조사는 &lt;strong&gt;현장이 보존된 상태에서 되도록 빨리&lt;/strong&gt;해야 한다.</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
@@ -3899,7 +3907,7 @@
       </c>
       <c r="AH22" s="32" t="inlineStr">
         <is>
-          <t>① 2.45 는 도수율을 10으로 나눈 환산도수율이다.&lt;br&gt;③ 215·245 는 계산과 맞지 않는다.&lt;br&gt;④ 245 는 도수율에 10을 곱한 값이다.</t>
+          <t>① 2.45는 도수율을 10으로 나눈 환산도수율이다.&lt;br&gt;③ 215·245는 계산과 맞지 않는다.&lt;br&gt;④ 245는 도수율에 10을 곱한 값이다.</t>
         </is>
       </c>
       <c r="AI22" s="32" t="inlineStr">
@@ -3989,11 +3997,15 @@
       </c>
       <c r="U23" s="32" t="inlineStr">
         <is>
-          <t>FT도에서 시스템의 신뢰도는 얼마인가? (단, 모든 부품의 발생확률은 0.1 이다.)</t>
+          <t>FT도에서 시스템의 신뢰도는 얼마인가? (단, 모든 부품의 발생확률은 0.1이다.)</t>
         </is>
       </c>
       <c r="V23" s="32" t="inlineStr"/>
-      <c r="W23" s="32" t="inlineStr"/>
+      <c r="W23" s="32" t="inlineStr">
+        <is>
+          <t>safe_A_2026_02_021_stem1.png</t>
+        </is>
+      </c>
       <c r="X23" s="32" t="inlineStr">
         <is>
           <t>0.0033</t>
@@ -4023,17 +4035,17 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>정상사상의 발생확률을 구한 뒤 &lt;strong&gt;1 에서 빼면 신뢰도&lt;/strong&gt;다. 부품마다 0.1 이므로 AND 게이트는 곱하고 OR 게이트는 $1 - ( 1 - q_{1} ) ( 1 - q_{2} )$ 로 묶어 올라간다. 이 FT 에서는 정상사상 확률이 0.0019 이므로 신뢰도는 &lt;strong&gt;0.9981&lt;/strong&gt;이다.</t>
+          <t>정상사상의 발생확률을 구한 뒤 &lt;strong&gt;1에서 빼면 신뢰도&lt;/strong&gt;다. 부품마다 0.1이므로 AND 게이트는 곱하고 OR 게이트는 $1 - ( 1 - q_{1} ) ( 1 - q_{2} )$로 묶어 올라간다. 이 FT 에서는 정상사상 확률이 0.0019이므로 신뢰도는 &lt;strong&gt;0.9981&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>① 0.0033 은 신뢰도가 아니라 고장확률 쪽 값이다.&lt;br&gt;② 0.0062 도 고장확률 쪽 값이다.&lt;br&gt;④ 0.9936 은 게이트를 잘못 묶었을 때 나온다.</t>
+          <t>① 0.0033은 신뢰도가 아니라 고장확률 쪽 값이다.&lt;br&gt;② 0.0062 도 고장확률 쪽 값이다.&lt;br&gt;④ 0.9936은 게이트를 잘못 묶었을 때 나온다.</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FT 의 정상사상 확률과 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AND 는 곱하고 OR 는 여집합으로 묶는다&lt;/strong&gt;. $R = 1 - P ( T )$ 로 마무리한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고장확률을 먼저 구하고 1에서 뺀다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FT의 정상사상 확률과 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AND는 곱하고 OR는 여집합으로 묶는다&lt;/strong&gt;. $R = 1 - P ( T )$로 마무리한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고장확률을 먼저 구하고 1에서 뺀다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4523,17 +4535,17 @@
       </c>
       <c r="AG27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Fail Operational&lt;/strong&gt;이다. 고장이 나도 &lt;strong&gt;다음 점검 때까지 기능을 유지&lt;/strong&gt; 한다. 셋 중 안전 수준이 가장 높다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Fail Safe 의 기능적 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;고장이 나면&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Fail Passive&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;곧바로 정지한다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 흔한 방식&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Fail Active&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경보를 내며 잠시 운전을 잇는다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경보 뒤 자동 정지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Fail Operational&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다음 점검까지 기능을 유지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다경로 구조 · 여러 대 병렬&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;Fail Operational&lt;/strong&gt;이다. 고장이 나도 &lt;strong&gt;다음 점검 때까지 기능을 유지&lt;/strong&gt; 한다. 셋 중 안전 수준이 가장 높다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Fail Safe의 기능적 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;고장이 나면&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Fail Passive&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;곧바로 정지한다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 흔한 방식&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Fail Active&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경보를 내며 잠시 운전을 잇는다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경보 뒤 자동 정지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Fail Operational&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다음 점검까지 기능을 유지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다경로 구조 · 여러 대 병렬&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH27" s="32" t="inlineStr">
         <is>
-          <t>① 「fail - soft」는 이 분류에 없는 이름이다.&lt;br&gt;② Fail Active 는 경보를 내며 잠시 운전을 잇는다.&lt;br&gt;④ Fail Passive 는 곧바로 정지한다.</t>
+          <t>① 「fail - soft」는 이 분류에 없는 이름이다.&lt;br&gt;② Fail Active는 경보를 내며 잠시 운전을 잇는다.&lt;br&gt;④ Fail Passive는 곧바로 정지한다.</t>
         </is>
       </c>
       <c r="AI27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Fail Safe 의 기능적 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Fail Safe 는 기계의 고장&lt;/strong&gt;, &lt;strong&gt;Fool Proof 는 사람의 실수&lt;/strong&gt;를 전제한다. 무엇을 전제하는지로 가른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Passive 정지 &amp;lt; Active 경보 후 잠시 &amp;lt; Operational 계속&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Fail Safe의 기능적 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Fail Safe는 기계의 고장&lt;/strong&gt;, &lt;strong&gt;Fool Proof는 사람의 실수&lt;/strong&gt;를 전제한다. 무엇을 전제하는지로 가른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Passive 정지 &amp;lt; Active 경보 후 잠시 &amp;lt; Operational 계속&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4615,7 @@
         <v>1</v>
       </c>
       <c r="Q28" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
@@ -4613,7 +4625,7 @@
       <c r="S28" s="32" t="inlineStr"/>
       <c r="T28" s="32" t="inlineStr">
         <is>
-          <t>원본 시행일 2021.08.14 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도1</t>
+          <t>원본 시행일 2021.08.14 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2</t>
         </is>
       </c>
       <c r="U28" s="32" t="inlineStr">
@@ -4621,7 +4633,11 @@
           <t>인간-기계 시스템의 설계 과정을 [보기]와 같이 분류할 때 다음 중 인간, 기계의 기능을 할당하는 단계는?</t>
         </is>
       </c>
-      <c r="V28" s="32" t="inlineStr"/>
+      <c r="V28" s="32" t="inlineStr">
+        <is>
+          <t>1단계 : 시스템의 목표와 성능명세 결정&lt;br&gt;2단계 : 시스템의 정의&lt;br&gt;3단계 : 기본 설계&lt;br&gt;4단계 : 인터페이스 설계&lt;br&gt;5단계 : 보조물 설계 혹은 편의수단 설계&lt;br&gt;6단계 : 평가</t>
+        </is>
+      </c>
       <c r="W28" s="32" t="inlineStr"/>
       <c r="X28" s="32" t="inlineStr">
         <is>
@@ -4778,7 +4794,7 @@
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
-          <t>① Risk Assessment 는 위험성만 재는 평가다.&lt;br&gt;② Risk Management 는 위험을 관리하는 활동이다.&lt;br&gt;③ Safety Assessment 는 설비의 안전성을 평가하는 것이다.</t>
+          <t>① Risk Assessment는 위험성만 재는 평가다.&lt;br&gt;② Risk Management는 위험을 관리하는 활동이다.&lt;br&gt;③ Safety Assessment는 설비의 안전성을 평가하는 것이다.</t>
         </is>
       </c>
       <c r="AI29" s="32" t="inlineStr">
@@ -4902,7 +4918,7 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>HAZOP 은 &lt;strong&gt;여러 분야 전문가가 모여 공정을 하나하나 훑는&lt;/strong&gt; 방식이라 &lt;strong&gt;시간과 비용이 많이 든다&lt;/strong&gt;. 오히려 단점이다.</t>
+          <t>HAZOP은 &lt;strong&gt;여러 분야 전문가가 모여 공정을 하나하나 훑는&lt;/strong&gt; 방식이라 &lt;strong&gt;시간과 비용이 많이 든다&lt;/strong&gt;. 오히려 단점이다.</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
@@ -5031,12 +5047,12 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;마모 고장기간&lt;/strong&gt;이다. 부품이 닳으면서 고장률이 점점 올라간다. 이 구간의 대책은 &lt;strong&gt;수명 전에 계획적으로 교체&lt;/strong&gt; 하는 예방보전이다.&lt;img src="safe_A_2026_02_029_exp1.png"&gt;&lt;em&gt;욕조곡선 — 구간마다 대책이 다르다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;마모 고장기간&lt;/strong&gt;이다. 부품이 닳으면서 고장률이 점점 올라간다. 이 구간의 대책은 &lt;strong&gt;수명 전에 계획적으로 교체&lt;/strong&gt;하는 예방보전이다.&lt;img src="safe_A_2026_02_029_exp1.png"&gt;&lt;em&gt;욕조곡선 — 구간마다 대책이 다르다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① 우발 고장기간은 고장률이 일정한 구간이다.&lt;br&gt;③ 초기 고장기간은 고장률이 줄어드는 구간이다.&lt;br&gt;④ Burn-in 은 초기 고장을 걸러내는 조치이지 기간의 이름이 아니다.</t>
+          <t>① 우발 고장기간은 고장률이 일정한 구간이다.&lt;br&gt;③ 초기 고장기간은 고장률이 줄어드는 구간이다.&lt;br&gt;④ Burn-in은 초기 고장을 걸러내는 조치이지 기간의 이름이 아니다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
@@ -5160,7 +5176,7 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>고장률이 &lt;strong&gt;일정&lt;/strong&gt; 하면 고장간격은 &lt;strong&gt;지수분포&lt;/strong&gt;를 따른다. 욕조곡선의 &lt;strong&gt;우발 고장기&lt;/strong&gt;가 이에 해당한다.</t>
+          <t>고장률이 &lt;strong&gt;일정&lt;/strong&gt;하면 고장간격은 &lt;strong&gt;지수분포&lt;/strong&gt;를 따른다. 욕조곡선의 &lt;strong&gt;우발 고장기&lt;/strong&gt;가 이에 해당한다.</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
@@ -5170,7 +5186,7 @@
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지수분포와 일정 고장률&lt;/strong&gt;&lt;br&gt;지수분포에서 신뢰도는 $R ( t ) = e^{-\lambda t}$ 이고 $\mathrm{MTBF} = 1 / \lambda$ 다. &lt;strong&gt;평균 고장률과 평균 수명은 역수 관계&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고장률이 일정하면 지수분포&lt;/u&gt;, $\mathrm{MTBF} = 1 / \lambda$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지수분포와 일정 고장률&lt;/strong&gt;&lt;br&gt;지수분포에서 신뢰도는 $R ( t ) = e^{-\lambda t}$이고 $\mathrm{MTBF} = 1 / \lambda$다. &lt;strong&gt;평균 고장률과 평균 수명은 역수 관계&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;고장률이 일정하면 지수분포&lt;/u&gt;, $\mathrm{MTBF} = 1 / \lambda$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5305,7 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>$\mathrm{MTBF} = 1 / \lambda$ 이므로 &lt;strong&gt;반비례&lt;/strong&gt;다. 고장률이 커질수록 수명은 짧아진다. 「정비례」는 방향이 거꾸로다.</t>
+          <t>$\mathrm{MTBF} = 1 / \lambda$이므로 &lt;strong&gt;반비례&lt;/strong&gt;다. 고장률이 커질수록 수명은 짧아진다. 「정비례」는 방향이 거꾸로다.</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
@@ -5299,7 +5315,7 @@
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;MTBF 와 고장률의 관계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;디레이팅(derating)&lt;/strong&gt;은 부품을 정격보다 낮은 부하로 쓰는 것이다. 여유를 두면 덜 상하므로 수명이 늘어난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MTBF} = 1 / \lambda$ — &lt;u&gt;반비례&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;MTBF와 고장률의 관계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;디레이팅(derating)&lt;/strong&gt;은 부품을 정격보다 낮은 부하로 쓰는 것이다. 여유를 두면 덜 상하므로 수명이 늘어난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MTBF} = 1 / \lambda$ — &lt;u&gt;반비례&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5434,7 @@
       </c>
       <c r="AG34" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;출입문&lt;/strong&gt;은 가장 큰 사람이 지날 수 있어야 하므로 &lt;strong&gt;최대집단치(95 %tile)&lt;/strong&gt;로 잡는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체측정치 응용의 세 원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대집단치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;95 %tile — 큰 사람 기준&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;출입문&lt;/u&gt; · 통로 · 비상구 · 침대 길이&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최소집단치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5 %tile — 작은 사람 기준&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;선반 높이 · 조작 버튼까지의 거리&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조절식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5~95 %tile 을 담게&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의자 높이 · 자동차 시트 · 책상&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;출입문&lt;/strong&gt;은 가장 큰 사람이 지날 수 있어야 하므로 &lt;strong&gt;최대집단치(95 %tile)&lt;/strong&gt;로 잡는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체측정치 응용의 세 원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대집단치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;95 %tile — 큰 사람 기준&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;출입문&lt;/u&gt; · 통로 · 비상구 · 침대 길이&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최소집단치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5 %tile — 작은 사람 기준&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;선반 높이 · 조작 버튼까지의 거리&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조절식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5~95 %tile을 담게&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의자 높이 · 자동차 시트 · 책상&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH34" s="32" t="inlineStr">
@@ -5676,17 +5692,17 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>옥내 또는 햇볕 없는 옥외는 $0.7 \times \text{자연습구} + 0.3 \times \text{흑구}$ 다. 두 계수의 합이 &lt;strong&gt;1&lt;/strong&gt;이 되어야 한다.&lt;img src="safe_A_2026_02_034_exp1.png"&gt;&lt;em&gt;WBGT 두 가지 식 — 햇볕이 있으면 건구온도가 들어온다&lt;/em&gt;</t>
+          <t>옥내 또는 햇볕 없는 옥외는 $0.7 \times \text{자연습구} + 0.3 \times \text{흑구}$다. 두 계수의 합이 &lt;strong&gt;1&lt;/strong&gt;이 되어야 한다.&lt;img src="safe_A_2026_02_034_exp1.png"&gt;&lt;em&gt;WBGT 두 가지 식 — 햇볕이 있으면 건구온도가 들어온다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>① 계수의 합이 0.9 로 1이 되지 않는다.&lt;br&gt;③ 계수의 합이 1이 되지 않는다.&lt;br&gt;④ 0.7 + 0.4 = 1.1 로 1을 넘는다.</t>
+          <t>① 계수의 합이 0.9로 1이 되지 않는다.&lt;br&gt;③ 계수의 합이 1이 되지 않는다.&lt;br&gt;④ 0.7 + 0.4 = 1.1로 1을 넘는다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;습구흑구온도지수(WBGT)&lt;/strong&gt;&lt;br&gt;햇볕이 있는 옥외는 $0.7 \times \text{자연습구} + 0.2 \times \text{흑구} + 0.1 \times \text{건구}$ 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자연습구 0.7 은 언제나 같고, 건구 0.1 은 햇볕이 있을 때만&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;습구흑구온도지수(WBGT)&lt;/strong&gt;&lt;br&gt;햇볕이 있는 옥외는 $0.7 \times \text{자연습구} + 0.2 \times \text{흑구} + 0.1 \times \text{건구}$다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자연습구 0.7은 언제나 같고, 건구 0.1은 햇볕이 있을 때만&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5950,7 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>FTA 는 각 사상의 확률을 넣으면 &lt;strong&gt;정량적 분석도 된다&lt;/strong&gt;. 「정성적 분석만」이 틀렸다.</t>
+          <t>FTA는 각 사상의 확률을 넣으면 &lt;strong&gt;정량적 분석도 된다&lt;/strong&gt;. 「정성적 분석만」이 틀렸다.</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
@@ -5944,7 +5960,7 @@
       </c>
       <c r="AI38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 와 FMEA 의 대비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA 는 연역적·하향식·정량 가능&lt;/strong&gt;, &lt;strong&gt;FMEA 는 귀납적·상향식·정성 중심&lt;/strong&gt;이다. 1962년 벨연구소가 미니트맨 미사일 발사 제어를 분석하며 만들었다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA 는 위에서 아래로, 정량도 된다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA와 FMEA의 대비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA는 연역적·하향식·정량 가능&lt;/strong&gt;, &lt;strong&gt;FMEA는 귀납적·상향식·정성 중심&lt;/strong&gt;이다. 1962년 벨연구소가 미니트맨 미사일 발사 제어를 분석하며 만들었다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA는 위에서 아래로, 정량도 된다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6063,17 +6079,17 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>$H = \log_{2} n = \log_{2} 64 = 6$ [bit] 다. &lt;strong&gt;2를 몇 번 곱해야 64가 되는가&lt;/strong&gt;를 묻는 것과 같다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;대안 수와 정보량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대안 수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정보량&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;2&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;켜짐/꺼짐&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;4&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;8&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;16&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;32&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;64&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$H = \log_{2} n = \log_{2} 64 = 6$ [bit]다. &lt;strong&gt;2를 몇 번 곱해야 64가 되는가&lt;/strong&gt;를 묻는 것과 같다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;대안 수와 정보량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대안 수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정보량&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;2&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;켜짐/꺼짐&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;4&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;8&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;16&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;32&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5 [bit]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;64&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>② 16 [bit] 는 대안이 65,536가지일 때다.&lt;br&gt;③ 32 [bit] 는 훨씬 큰 값이다.&lt;br&gt;④ 64 [bit] 는 대안 수를 그대로 적은 것이다.</t>
+          <t>② 16 [bit]는 대안이 65,536가지일 때다.&lt;br&gt;③ 32 [bit]는 훨씬 큰 값이다.&lt;br&gt;④ 64 [bit]는 대안 수를 그대로 적은 것이다.</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정보량 $H = \log_{2} n$&lt;/strong&gt;&lt;br&gt;확률이 서로 다르면 $H = \sum p_{i} \log_{2} ( 1 / p_{i} )$ 로 구한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;2를 몇 번 곱해야 그 수가 되는가&lt;/u&gt; — 64는 6번.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정보량 $H = \log_{2} n$&lt;/strong&gt;&lt;br&gt;확률이 서로 다르면 $H = \sum p_{i} \log_{2} ( 1 / p_{i} )$로 구한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;2를 몇 번 곱해야 그 수가 되는가&lt;/u&gt; — 64는 6번.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6208,12 @@
       </c>
       <c r="AG40" s="32" t="inlineStr">
         <is>
-          <t>데시벨은 로그 값이라 &lt;strong&gt;그냥 더하지 못한다&lt;/strong&gt;. 세기로 되돌려 더한 뒤 다시 데시벨로 바꾼다. $L = 10 \log ( 10^{8.0} + 10^{8.6} + 10^{7.8} ) \fallingdotseq 87.5$ [dB] 다.</t>
+          <t>데시벨은 로그 값이라 &lt;strong&gt;그냥 더하지 못한다&lt;/strong&gt;. 세기로 되돌려 더한 뒤 다시 데시벨로 바꾼다. $L = 10 \log ( 10^{8.0} + 10^{8.6} + 10^{7.8} ) \fallingdotseq 87.5$ [dB]다.</t>
         </is>
       </c>
       <c r="AH40" s="32" t="inlineStr">
         <is>
-          <t>① 81.3 은 계산과 맞지 않는다.&lt;br&gt;② 85.5 는 세 값을 단순 평균했을 때에 가깝다.&lt;br&gt;④ 90.3 은 세 값을 그대로 더했을 때 쪽에 가깝다.</t>
+          <t>① 81.3은 계산과 맞지 않는다.&lt;br&gt;② 85.5는 세 값을 단순 평균했을 때에 가깝다.&lt;br&gt;④ 90.3은 세 값을 그대로 더했을 때 쪽에 가깝다.</t>
         </is>
       </c>
       <c r="AI40" s="32" t="inlineStr">
@@ -6460,7 +6476,7 @@
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;화학설비의 안전성 평가&lt;/strong&gt;&lt;br&gt;6단계는 &lt;strong&gt;관계 자료의 정비 → 정성적 평가 → 정량적 평가 → 안전대책 → 재해정보에 의한 재평가 → FTA 에 의한 재평가&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 정량적 평가 다섯은 「&lt;u&gt;물 · 용 · 온 · 압 · 조&lt;/u&gt;」.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;화학설비의 안전성 평가&lt;/strong&gt;&lt;br&gt;6단계는 &lt;strong&gt;관계 자료의 정비 → 정성적 평가 → 정량적 평가 → 안전대책 → 재해정보에 의한 재평가 → FTA에 의한 재평가&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; 정량적 평가 다섯은 「&lt;u&gt;물 · 용 · 온 · 압 · 조&lt;/u&gt;」.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6605,7 @@
       </c>
       <c r="AI43" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;플레이너 작업의 안전대책&lt;/strong&gt;&lt;br&gt;플레이너는 &lt;strong&gt;테이블이 왕복&lt;/strong&gt; 하고 셰이퍼는 &lt;strong&gt;바이트가 왕복&lt;/strong&gt; 한다. 둘 다 왕복 구간에 사람이 서지 않도록 &lt;strong&gt;방책&lt;/strong&gt;을 세운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;칩 브레이커는 칩을 끊는다&lt;/u&gt; — 길게 만드는 장치가 아니다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;플레이너 작업의 안전대책&lt;/strong&gt;&lt;br&gt;플레이너는 &lt;strong&gt;테이블이 왕복&lt;/strong&gt;하고 셰이퍼는 &lt;strong&gt;바이트가 왕복&lt;/strong&gt;한다. 둘 다 왕복 구간에 사람이 서지 않도록 &lt;strong&gt;방책&lt;/strong&gt;을 세운다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;칩 브레이커는 칩을 끊는다&lt;/u&gt; — 길게 만드는 장치가 아니다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7240,7 @@
       </c>
       <c r="AG48" s="32" t="inlineStr">
         <is>
-          <t>게이트 가드식은 &lt;strong&gt;문을 닫아야만 동작&lt;/strong&gt; 하는 것이 연동구조다. 「닫지 않아도 동작」하면 방호장치가 아니다.</t>
+          <t>게이트 가드식은 &lt;strong&gt;문을 닫아야만 동작&lt;/strong&gt;하는 것이 연동구조다. 「닫지 않아도 동작」하면 방호장치가 아니다.</t>
         </is>
       </c>
       <c r="AH48" s="32" t="inlineStr">
@@ -7363,7 +7379,7 @@
       </c>
       <c r="AI49" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자분탐상시험(MT)&lt;/strong&gt;&lt;br&gt;표면 계열 셋을 가른다 — &lt;strong&gt;MT 는 자석에 붙는 것, ET 는 전기가 통하는 것, PT 는 아무거나(열린 결함만)&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자화해서 새어 나오는 자속을 보면 MT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자분탐상시험(MT)&lt;/strong&gt;&lt;br&gt;표면 계열 셋을 가른다 — &lt;strong&gt;MT는 자석에 붙는 것, ET는 전기가 통하는 것, PT는 아무거나(열린 결함만)&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자화해서 새어 나오는 자속을 보면 MT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7740,17 +7756,17 @@
       </c>
       <c r="AG52" s="32" t="inlineStr">
         <is>
-          <t>$D_{m} = 1.6 T_{m}$, $T_{m} = ( \dfrac{1}{\text{클러치 개소수}} + \dfrac{1}{2} ) \times \dfrac{60 {,} 000}{\mathrm{SPM}}$ 이다. $T_{m} = ( 1 / 6 + 1 / 2 ) \times 60 {,} 000 / 200 = 0.667 \times 300 = 200$ [ms] 이므로 $D_{m} = 1.6 \times 200 = 320$ [mm] 다.</t>
+          <t>$D_{m} = 1.6 T_{m}$, $T_{m} = ( \dfrac{1}{\text{클러치 개소수}} + \dfrac{1}{2} ) \times \dfrac{60 {,} 000}{\mathrm{SPM}}$이다. $T_{m} = ( 1 / 6 + 1 / 2 ) \times 60 {,} 000 / 200 = 0.667 \times 300 = 200$ [ms]이므로 $D_{m} = 1.6 \times 200 = 320$ [mm]다.</t>
         </is>
       </c>
       <c r="AH52" s="32" t="inlineStr">
         <is>
-          <t>① 120 [mm] 는 계산과 맞지 않는다.&lt;br&gt;② 200 [mm] 는 $T_{m}$ 값 자체다. 1.6 을 곱하는 것을 잊으면 이 답을 고른다.&lt;br&gt;④ 400 [mm] 는 $T_{m}$ 를 250 [ms] 로 잡았을 때 나온다.</t>
+          <t>① 120 [mm]는 계산과 맞지 않는다.&lt;br&gt;② 200 [mm]는 $T_{m}$ 값 자체다. 1.6을 곱하는 것을 잊으면 이 답을 고른다.&lt;br&gt;④ 400 [mm]는 $T_{m}$를 250 [ms]로 잡았을 때 나온다.</t>
         </is>
       </c>
       <c r="AI52" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;계수 &lt;strong&gt;1.6&lt;/strong&gt;은 사람 손의 접근속도 &lt;strong&gt;1.6 [m/s]&lt;/strong&gt;에서 왔다. 광전자식은 $D = 1.6 ( T_{l} + T_{s} )$ 로 식이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D_{m} = 1.6 T_{m}$, $T_{m}$ 은 &lt;u&gt;(1/개소수 + 1/2) × 60,000/SPM&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;계수 &lt;strong&gt;1.6&lt;/strong&gt;은 사람 손의 접근속도 &lt;strong&gt;1.6 [m/s]&lt;/strong&gt;에서 왔다. 광전자식은 $D = 1.6 ( T_{l} + T_{s} )$로 식이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D_{m} = 1.6 T_{m}$, $T_{m}$은 &lt;u&gt;(1/개소수 + 1/2) × 60,000/SPM&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8798,7 @@
       </c>
       <c r="AI60" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제132조 — 양중기의 범위&lt;/strong&gt;&lt;br&gt;크레인은 &lt;strong&gt;정격하중 0.5톤 이상&lt;/strong&gt;, 이삿짐운반용 리프트는 &lt;strong&gt;적재하중 0.1톤 이상&lt;/strong&gt; 이라야 양중기로 본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이삿짐 리프트는 0.1톤 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항은 가답안이 ③이었으나 확정답안에서 ③④ 모두 정답 처리되었다. 선택지 ③의 표현이 「이삿짐운반용 리프트」와 「화물용 엘리베이터」를 뒤섞어 놓아 생긴 일이다. &lt;u&gt;적재하중 0.1톤 미만은 양중기가 아니다&lt;/u&gt;라는 기준만 정확히 잡으면 된다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C132%EC%A1%B0" target="_blank"&gt;제132조(양중기)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 양중기란 다음 각 호의 기계를 말한다. &amp;lt;개정 2019.4.19&amp;gt;&lt;br&gt; 1. 크레인[호이스트(hoist)를 포함한다]&lt;br&gt; 2. 이동식 크레인&lt;br&gt;▶  3. 리프트(&lt;strong&gt;이삿짐운반용 리프트&lt;/strong&gt;의 경우에는 적재하중이 &lt;strong&gt;0.1톤 이상&lt;/strong&gt;인 것으로 한정한다)&lt;br&gt; 4. 곤돌라&lt;br&gt; 5. 승강기&lt;br&gt;② 제1항 각 호의 기계의 뜻은 다음 각 호와 같다. &amp;lt;개정 2019.4.19, 2021.11.19, 2022.10.18&amp;gt;&lt;br&gt; 1. "크레인"이란 동력을 사용하여 중량물을 매달아 상하 및 좌우(수평 또는 선회를 말한다)로 운반하는 것을 목적으로 하는 기계 또는 기계장치를 말하며, "호이스트"란 훅이나 그 밖의 달기구 등을 사용하여 화물을 권상 및 횡행 또는 권상동작만을 하여 양중하는 것을 말한다.&lt;br&gt; 2. "이동식 크레인"이란 원동기를 내장하고 있는 것으로서 불특정 장소에 스스로 이동할 수 있는 크레인으로 동력을 사용하여 중량물을 매달아 상하 및 좌우(수평 또는 선회를 말한다)로 운반하는 설비로서 「건설기계관리법」을 적용 받는 기중기 또는 「자동차관리법」제3조에 따른 화물ㆍ특수자동차의 작업부에 탑재하여 화물운반 등에 사용하는 기계 또는 기계장치를 말한다.&lt;br&gt; 3. "리프트"란 동력을 사용하여 사람이나 화물을 운반하는 것을 목적으로 하는 기계설비로서 다음 각 목의 것을 말한다.&lt;br&gt; 가. 건설용 리프트: 동력을 사용하여 가이드레일(운반구를 지지하여 상승 및 하강 동작을 안내하는 레일)을 따라 상하로 움직이는 운반구를 매달아 사람이나 화물을 운반할 수 있는 설비 또는 이와 유사한 구조 및 성능을 가진 것으로 건설현장에서 사용하는 것&lt;br&gt; 나. 산업용 리프트: 동력을 사용하여 가이드레일을 따라 상하로 움직이는 운반구를 매달아 화물을 운반할 수 있는 설비 또는 이와 유사한 구조 및 성능을 가진 것으로 건설현장 외의 장소에서 사용하는 것&lt;br&gt; 다. 자동차정비용 리프트: 동력을 사용하여 가이드레일을 따라 움직이는 지지대로 자동차 등을 일정한 높이로 올리거나 내리는 구조의 리프트로서 자동차 정비에 사용하는 것&lt;br&gt;▶  라. &lt;strong&gt;이삿짐운반용 리프트&lt;/strong&gt;: 연장 및 축소가 가능하고 끝단을 건축물 등에 지지하는 구조의 사다리형 붐에 따라 동력을 사용하여 움직이는 운반구를 매달아 화물을 운반하는 설비로서 화물자동차 등 차량 위에 탑재하여 이삿짐 운반 등에 사용하는 것&lt;br&gt; 4. "곤돌라"란 달기발판 또는 운반구, 승강장치, 그 밖의 장치 및 이들에 부속된 기계부품에 의하여 구성되고, 와이어로프 또는 달기강선에 의하여 달기발판 또는 운반구가 전용 승강장치에 의하여 오르내리는 설비를 말한다.&lt;br&gt; 5. "승강기"란 건축물이나 고정된 시설물에 설치되어 일정한 경로에 따라 사람이나 화물을 승강장으로 옮기는 데에 사용되는 설비로서 다음 각 목의 것을 말한다.&lt;br&gt; 가. 승객용 엘리베이터: 사람의 운송에 적합하게 제조ㆍ설치된 엘리베이터&lt;br&gt; 나. 승객화물용 엘리베이터: 사람의 운송과 화물 운반을 겸용하는데 적합하게 제조ㆍ설치된 엘리베이터&lt;br&gt; 다. 화물용 엘리베이터: 화물 운반에 적합하게 제조ㆍ설치된 엘리베이터로서 조작자 또는 화물취급자 1명은 탑승할 수 있는 것(적재용량이 300킬로그램 미만인 것은 제외한다)&lt;br&gt; 라. 소형화물용 엘리베이터: 음식물이나 서적 등 소형 화물의 운반에 적합하게 제조ㆍ설치된 엘리베이터로서 사람의 탑승이 금지된 것&lt;br&gt; 마. 에스컬레이터: 일정한 경사로 또는 수평로를 따라 위ㆍ아래 또는 옆으로 움직이는 디딤판을 통해 사람이나 화물을 승강장으로 운송시키는 설비&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제132조 — 양중기의 범위&lt;/strong&gt;&lt;br&gt;크레인은 &lt;strong&gt;정격하중 0.5톤 이상&lt;/strong&gt;, 이삿짐운반용 리프트는 &lt;strong&gt;적재하중 0.1톤 이상&lt;/strong&gt;이라야 양중기로 본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이삿짐 리프트는 0.1톤 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항은 가답안이 ③이었으나 확정답안에서 ③④ 모두 정답 처리되었다. 선택지 ③의 표현이 「이삿짐운반용 리프트」와 「화물용 엘리베이터」를 뒤섞어 놓아 생긴 일이다. &lt;u&gt;적재하중 0.1톤 미만은 양중기가 아니다&lt;/u&gt;라는 기준만 정확히 잡으면 된다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C132%EC%A1%B0" target="_blank"&gt;제132조(양중기)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 양중기란 다음 각 호의 기계를 말한다. &amp;lt;개정 2019.4.19&amp;gt;&lt;br&gt; 1. 크레인[호이스트(hoist)를 포함한다]&lt;br&gt; 2. 이동식 크레인&lt;br&gt;▶  3. 리프트(&lt;strong&gt;이삿짐운반용 리프트&lt;/strong&gt;의 경우에는 적재하중이 &lt;strong&gt;0.1톤 이상&lt;/strong&gt;인 것으로 한정한다)&lt;br&gt; 4. 곤돌라&lt;br&gt; 5. 승강기&lt;br&gt;② 제1항 각 호의 기계의 뜻은 다음 각 호와 같다. &amp;lt;개정 2019.4.19, 2021.11.19, 2022.10.18&amp;gt;&lt;br&gt; 1. "크레인"이란 동력을 사용하여 중량물을 매달아 상하 및 좌우(수평 또는 선회를 말한다)로 운반하는 것을 목적으로 하는 기계 또는 기계장치를 말하며, "호이스트"란 훅이나 그 밖의 달기구 등을 사용하여 화물을 권상 및 횡행 또는 권상동작만을 하여 양중하는 것을 말한다.&lt;br&gt; 2. "이동식 크레인"이란 원동기를 내장하고 있는 것으로서 불특정 장소에 스스로 이동할 수 있는 크레인으로 동력을 사용하여 중량물을 매달아 상하 및 좌우(수평 또는 선회를 말한다)로 운반하는 설비로서 「건설기계관리법」을 적용 받는 기중기 또는 「자동차관리법」제3조에 따른 화물ㆍ특수자동차의 작업부에 탑재하여 화물운반 등에 사용하는 기계 또는 기계장치를 말한다.&lt;br&gt; 3. "리프트"란 동력을 사용하여 사람이나 화물을 운반하는 것을 목적으로 하는 기계설비로서 다음 각 목의 것을 말한다.&lt;br&gt; 가. 건설용 리프트: 동력을 사용하여 가이드레일(운반구를 지지하여 상승 및 하강 동작을 안내하는 레일)을 따라 상하로 움직이는 운반구를 매달아 사람이나 화물을 운반할 수 있는 설비 또는 이와 유사한 구조 및 성능을 가진 것으로 건설현장에서 사용하는 것&lt;br&gt; 나. 산업용 리프트: 동력을 사용하여 가이드레일을 따라 상하로 움직이는 운반구를 매달아 화물을 운반할 수 있는 설비 또는 이와 유사한 구조 및 성능을 가진 것으로 건설현장 외의 장소에서 사용하는 것&lt;br&gt; 다. 자동차정비용 리프트: 동력을 사용하여 가이드레일을 따라 움직이는 지지대로 자동차 등을 일정한 높이로 올리거나 내리는 구조의 리프트로서 자동차 정비에 사용하는 것&lt;br&gt;▶  라. &lt;strong&gt;이삿짐운반용 리프트&lt;/strong&gt;: 연장 및 축소가 가능하고 끝단을 건축물 등에 지지하는 구조의 사다리형 붐에 따라 동력을 사용하여 움직이는 운반구를 매달아 화물을 운반하는 설비로서 화물자동차 등 차량 위에 탑재하여 이삿짐 운반 등에 사용하는 것&lt;br&gt; 4. "곤돌라"란 달기발판 또는 운반구, 승강장치, 그 밖의 장치 및 이들에 부속된 기계부품에 의하여 구성되고, 와이어로프 또는 달기강선에 의하여 달기발판 또는 운반구가 전용 승강장치에 의하여 오르내리는 설비를 말한다.&lt;br&gt; 5. "승강기"란 건축물이나 고정된 시설물에 설치되어 일정한 경로에 따라 사람이나 화물을 승강장으로 옮기는 데에 사용되는 설비로서 다음 각 목의 것을 말한다.&lt;br&gt; 가. 승객용 엘리베이터: 사람의 운송에 적합하게 제조ㆍ설치된 엘리베이터&lt;br&gt; 나. 승객화물용 엘리베이터: 사람의 운송과 화물 운반을 겸용하는데 적합하게 제조ㆍ설치된 엘리베이터&lt;br&gt; 다. 화물용 엘리베이터: 화물 운반에 적합하게 제조ㆍ설치된 엘리베이터로서 조작자 또는 화물취급자 1명은 탑승할 수 있는 것(적재용량이 300킬로그램 미만인 것은 제외한다)&lt;br&gt; 라. 소형화물용 엘리베이터: 음식물이나 서적 등 소형 화물의 운반에 적합하게 제조ㆍ설치된 엘리베이터로서 사람의 탑승이 금지된 것&lt;br&gt; 마. 에스컬레이터: 일정한 경사로 또는 수평로를 따라 위ㆍ아래 또는 옆으로 움직이는 디딤판을 통해 사람이나 화물을 승강장으로 운송시키는 설비&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -9164,12 +9180,12 @@
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>① 동작시간 0.01초라는 기준은 없다.&lt;br&gt;③ 30 [mA] 는 일반 장소의 기준이다.&lt;br&gt;④ 30 [mA] 와 0.01초 둘 다 어긋난다.</t>
+          <t>① 동작시간 0.01초라는 기준은 없다.&lt;br&gt;③ 30 [mA]는 일반 장소의 기준이다.&lt;br&gt;④ 30 [mA]와 0.01초 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;한국전기설비규정(KEC) 211.2.4 — 누전차단기의 시설&lt;/strong&gt;&lt;br&gt;30 [mA]·0.03초는 Dalziel 의 심실세동 한계 $I = 165 / \sqrt{T}$ 에서 나온 값이다. 물기가 있으면 그 여유가 사라진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일반 30, 물기 15&lt;/u&gt; — 시간은 둘 다 0.03초.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;한국전기설비규정(KEC) 211.2.4 — 누전차단기의 시설&lt;/strong&gt;&lt;br&gt;30 [mA]·0.03초는 Dalziel의 심실세동 한계 $I = 165 / \sqrt{T}$에서 나온 값이다. 물기가 있으면 그 여유가 사라진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일반 30, 물기 15&lt;/u&gt; — 시간은 둘 다 0.03초.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9273,11 @@
           <t>어느 변전소에서 고장전류가 유입되었을 때 도전성 구조물과 그 부근 지표상의 점과의 사이(약 1m)의 허용접촉전압은 약 몇 V 인가? (단, 심실세동전류, 인체의 저항 1000Ω, 지표면의 저항률 150Ω⸱m, 통전시간을 1초로 한다.)</t>
         </is>
       </c>
-      <c r="V64" s="32" t="inlineStr"/>
+      <c r="V64" s="32" t="inlineStr">
+        <is>
+          <t>심실세동전류   I_k = 0.165 / √t   [A]</t>
+        </is>
+      </c>
       <c r="W64" s="32" t="inlineStr"/>
       <c r="X64" s="32" t="inlineStr">
         <is>
@@ -9288,12 +9308,12 @@
       </c>
       <c r="AG64" s="32" t="inlineStr">
         <is>
-          <t>$E = ( R_{b} + 1.5 \rho_{s} ) \times I_{k}$ 다. $I_{k} = 0.165 / \sqrt{1} = 0.165$ [A] 이므로 $E = ( 1 {,} 000 + 1.5 \times 150 ) \times 0.165 = 1 {,} 225 \times 0.165 \fallingdotseq 202$ [V] 다.</t>
+          <t>$E = ( R_{b} + 1.5 \rho_{s} ) \times I_{k}$다. $I_{k} = 0.165 / \sqrt{1} = 0.165$ [A]이므로 $E = ( 1 {,} 000 + 1.5 \times 150 ) \times 0.165 = 1 {,} 225 \times 0.165 \fallingdotseq 202$ [V]다.</t>
         </is>
       </c>
       <c r="AH64" s="32" t="inlineStr">
         <is>
-          <t>① 164 는 지표면 저항률을 빼고 계산했을 때에 가깝다.&lt;br&gt;② 186 은 계수를 1.0 으로 잡았을 때 나온다.&lt;br&gt;④ 228 은 계수를 2.0 으로 잡았을 때 나온다.</t>
+          <t>① 164는 지표면 저항률을 빼고 계산했을 때에 가깝다.&lt;br&gt;② 186은 계수를 1.0으로 잡았을 때 나온다.&lt;br&gt;④ 228은 계수를 2.0으로 잡았을 때 나온다.</t>
         </is>
       </c>
       <c r="AI64" s="32" t="inlineStr">
@@ -9417,7 +9437,7 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>제3종은 &lt;strong&gt;50 [V] 이하&lt;/strong&gt;다. 35 [V] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;접촉상태에 따른 허용접촉전압&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종별&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접촉 상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;허용접촉전압&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;제1종&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물에 젖어 있거나 인체가 계속 접촉&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;제2종&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;금속제 구조물에 인체 일부가 상시 접촉&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;제3종&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;건조한 통상의 인체 상태로 접촉&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;제4종&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;접촉 위험이 거의 없는 상태&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제한 없음&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>제3종은 &lt;strong&gt;50 [V] 이하&lt;/strong&gt;다. 35 [V]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;접촉상태에 따른 허용접촉전압&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종별&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접촉 상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;허용접촉전압&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;제1종&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물에 젖어 있거나 인체가 계속 접촉&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;제2종&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;금속제 구조물에 인체 일부가 상시 접촉&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;제3종&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;건조한 통상의 인체 상태로 접촉&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;제4종&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;접촉 위험이 거의 없는 상태&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제한 없음&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
@@ -9675,7 +9695,7 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>생략할 수 있는 것은 &lt;strong&gt;대지전압 150 [V] 이하&lt;/strong&gt;를 물기 없는 곳에 시설하는 경우다. 200 [V] 는 이를 넘으므로 &lt;strong&gt;누전차단기를 달아야 한다&lt;/strong&gt;.</t>
+          <t>생략할 수 있는 것은 &lt;strong&gt;대지전압 150 [V] 이하&lt;/strong&gt;를 물기 없는 곳에 시설하는 경우다. 200 [V]는 이를 넘으므로 &lt;strong&gt;누전차단기를 달아야 한다&lt;/strong&gt;.</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
@@ -9685,7 +9705,7 @@
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제304조 — 누전차단기의 설치 예외&lt;/strong&gt;&lt;br&gt;생략의 논리는 하나다 — &lt;strong&gt;누전차단기가 없어도 감전될 길이 없는 경우&lt;/strong&gt;. 건조·절연·이중절연·비접지방식이 모두 그런 경우다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대지전압 150 [V] 이하&lt;/u&gt; 라야 생략 — 200 은 안 된다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C304%EC%A1%B0" target="_blank"&gt;제304조(누전차단기에 의한 감전방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 다음 각 호의 전기 기계ㆍ기구에 대하여 누전에 의한 감전위험을 방지하기 위하여 해당 전로의 정격에 적합하고 감도(전류 등에 반응하는 정도)가 양호하며 확실하게 작동하는 감전방지용 누전차단기를 설치해야 한다. &amp;lt;개정 2021.11.19&amp;gt;&lt;br&gt; 1. 대지전압이 150볼트를 초과하는 이동형 또는 휴대형 전기기계ㆍ기구&lt;br&gt; 2. 물 등 도전성이 높은 액체가 있는 습윤장소에서 사용하는 저압(1.5천볼트 이하 직류전압이나 1천볼트 이하의 교류전압을 말한다)용 전기기계ㆍ기구&lt;br&gt; 3. 철판ㆍ철골 위 등 도전성이 높은 장소에서 사용하는 이동형 또는 휴대형 전기기계ㆍ기구&lt;br&gt; 4. 임시배선의 전로가 설치되는 장소에서 사용하는 이동형 또는 휴대형 전기기계ㆍ기구&lt;br&gt;② 사업주는 제1항에 따라 감전방지용 누전차단기를 설치하기 어려운 경우에는 작업시작 전에 접지선의 연결 및 접속부 상태 등이 적합한지 확실하게 점검하여야 한다.&lt;br&gt;③ 다음 각 호의 어느 하나에 해당하는 경우에는 제1항과 제2항을 적용하지 않는다. &amp;lt;개정 2019.1.31, 2021.11.19&amp;gt;&lt;br&gt; 1. 「전기용품 및 생활용품 안전관리법」이 적용되는 이중절연 또는 이와 같은 수준 이상으로 보호되는 구조로 된 전기기계ㆍ기구&lt;br&gt; 2. 절연대 위 등과 같이 감전위험이 없는 장소에서 사용하는 전기기계ㆍ기구&lt;br&gt; 3. 비접지방식의 전로&lt;br&gt;④ 사업주는 제1항에 따라 전기기계ㆍ기구를 사용하기 전에 해당 누전차단기의 작동상태를 점검하고 이상이 발견되면 즉시 보수하거나 교환하여야 한다.&lt;br&gt;▶ ⑤ 사업주는 제1항에 따라 설치한 누전차단기를 접속하는 경우에 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 전기기계ㆍ기구에 설치되어 있는 누전차단기는 정격감도전류가 30밀리암페어 이하이고 작동시간은 0.03초 이내일 것. 다만, 정격전부하전류가 50암페어 이상인 전기기계ㆍ기구에 접속되는 누전차단기는 오작동을 방지하기 위하여 정격감도전류는 200밀리암페어 이하로, 작동시간은 0.1초 이내로 할 수 있다.&lt;br&gt; 2. 분기회로 또는 전기기계ㆍ기구마다 누전차단기를 접속할 것. 다만, 평상시 누설전류가 매우 적은 소용량부하의 전로에는 분기회로에 일괄하여 접속할 수 있다.&lt;br&gt; 3. 누전차단기는 배전반 또는 분전반 내에 접속하거나 꽂음접속기형 누전차단기를 콘센트에 접속하는 등 파손이나 감전사고를 방지할 수 있는 장소에 접속할 것&lt;br&gt; 4. 지락보호전용 기능만 있는 누전차단기는 과전류를 차단하는 퓨즈나 차단기 등과 조합하여 접속할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제304조 — 누전차단기의 설치 예외&lt;/strong&gt;&lt;br&gt;생략의 논리는 하나다 — &lt;strong&gt;누전차단기가 없어도 감전될 길이 없는 경우&lt;/strong&gt;. 건조·절연·이중절연·비접지방식이 모두 그런 경우다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대지전압 150 [V] 이하&lt;/u&gt;라야 생략 — 200은 안 된다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C304%EC%A1%B0" target="_blank"&gt;제304조(누전차단기에 의한 감전방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 다음 각 호의 전기 기계ㆍ기구에 대하여 누전에 의한 감전위험을 방지하기 위하여 해당 전로의 정격에 적합하고 감도(전류 등에 반응하는 정도)가 양호하며 확실하게 작동하는 감전방지용 누전차단기를 설치해야 한다. &amp;lt;개정 2021.11.19&amp;gt;&lt;br&gt; 1. 대지전압이 150볼트를 초과하는 이동형 또는 휴대형 전기기계ㆍ기구&lt;br&gt; 2. 물 등 도전성이 높은 액체가 있는 습윤장소에서 사용하는 저압(1.5천볼트 이하 직류전압이나 1천볼트 이하의 교류전압을 말한다)용 전기기계ㆍ기구&lt;br&gt; 3. 철판ㆍ철골 위 등 도전성이 높은 장소에서 사용하는 이동형 또는 휴대형 전기기계ㆍ기구&lt;br&gt; 4. 임시배선의 전로가 설치되는 장소에서 사용하는 이동형 또는 휴대형 전기기계ㆍ기구&lt;br&gt;② 사업주는 제1항에 따라 감전방지용 누전차단기를 설치하기 어려운 경우에는 작업시작 전에 접지선의 연결 및 접속부 상태 등이 적합한지 확실하게 점검하여야 한다.&lt;br&gt;③ 다음 각 호의 어느 하나에 해당하는 경우에는 제1항과 제2항을 적용하지 않는다. &amp;lt;개정 2019.1.31, 2021.11.19&amp;gt;&lt;br&gt; 1. 「전기용품 및 생활용품 안전관리법」이 적용되는 이중절연 또는 이와 같은 수준 이상으로 보호되는 구조로 된 전기기계ㆍ기구&lt;br&gt; 2. 절연대 위 등과 같이 감전위험이 없는 장소에서 사용하는 전기기계ㆍ기구&lt;br&gt; 3. 비접지방식의 전로&lt;br&gt;④ 사업주는 제1항에 따라 전기기계ㆍ기구를 사용하기 전에 해당 누전차단기의 작동상태를 점검하고 이상이 발견되면 즉시 보수하거나 교환하여야 한다.&lt;br&gt;▶ ⑤ 사업주는 제1항에 따라 설치한 누전차단기를 접속하는 경우에 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 전기기계ㆍ기구에 설치되어 있는 누전차단기는 정격감도전류가 30밀리암페어 이하이고 작동시간은 0.03초 이내일 것. 다만, 정격전부하전류가 50암페어 이상인 전기기계ㆍ기구에 접속되는 누전차단기는 오작동을 방지하기 위하여 정격감도전류는 200밀리암페어 이하로, 작동시간은 0.1초 이내로 할 수 있다.&lt;br&gt; 2. 분기회로 또는 전기기계ㆍ기구마다 누전차단기를 접속할 것. 다만, 평상시 누설전류가 매우 적은 소용량부하의 전로에는 분기회로에 일괄하여 접속할 수 있다.&lt;br&gt; 3. 누전차단기는 배전반 또는 분전반 내에 접속하거나 꽂음접속기형 누전차단기를 콘센트에 접속하는 등 파손이나 감전사고를 방지할 수 있는 장소에 접속할 것&lt;br&gt; 4. 지락보호전용 기능만 있는 누전차단기는 과전류를 차단하는 퓨즈나 차단기 등과 조합하여 접속할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9829,7 @@
       </c>
       <c r="AH68" s="32" t="inlineStr">
         <is>
-          <t>② 6 [m] 는 35 [kV] 초과 160 [kV] 이하의 기준이다.&lt;br&gt;③ 7 [m] 라는 기준은 없다.&lt;br&gt;④ 9 [m] 도 기준에 없다.</t>
+          <t>② 6 [m]는 35 [kV] 초과 160 [kV] 이하의 기준이다.&lt;br&gt;③ 7 [m]라는 기준은 없다.&lt;br&gt;④ 9 [m] 도 기준에 없다.</t>
         </is>
       </c>
       <c r="AI68" s="32" t="inlineStr">
@@ -9933,17 +9953,17 @@
       </c>
       <c r="AG69" s="32" t="inlineStr">
         <is>
-          <t>$W = \dfrac{1}{2} C V^{2}$ 에서 $V = \sqrt{2 W / C}$ 다. $V = \sqrt{2 \times 0.2 \times 10^{-3} / ( 10 \times 10^{-12} )} = \sqrt{4 \times 10^{7}} \fallingdotseq 6 {,} 325$ [V] 다.</t>
+          <t>$W = \dfrac{1}{2} C V^{2}$에서 $V = \sqrt{2 W / C}$다. $V = \sqrt{2 \times 0.2 \times 10^{-3} / ( 10 \times 10^{-12} )} = \sqrt{4 \times 10^{7}} \fallingdotseq 6 {,} 325$ [V]다.</t>
         </is>
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>② 5225 는 에너지를 작게 잡았을 때 나온다.&lt;br&gt;③ 4135 도 계산과 맞지 않는다.&lt;br&gt;④ 3035 는 제곱근을 빼먹었을 때 쪽에 가깝다.</t>
+          <t>② 5225는 에너지를 작게 잡았을 때 나온다.&lt;br&gt;③ 4135 도 계산과 맞지 않는다.&lt;br&gt;④ 3035는 제곱근을 빼먹었을 때 쪽에 가깝다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 에너지와 착화한계전압&lt;/strong&gt;&lt;br&gt;$W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} Q V$. &lt;strong&gt;정전용량이 작을수록 같은 에너지를 내는 데 더 높은 전압&lt;/strong&gt;이 필요하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \sqrt{2 W / C}$ — 단위를 [J] 와 [F] 로 맞춘다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 에너지와 착화한계전압&lt;/strong&gt;&lt;br&gt;$W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} Q V$. &lt;strong&gt;정전용량이 작을수록 같은 에너지를 내는 데 더 높은 전압&lt;/strong&gt;이 필요하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \sqrt{2 W / C}$ — 단위를 [J]와 [F]로 맞춘다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10062,17 +10082,17 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>등급 2의 직류 최대사용전압은 &lt;strong&gt;25,500 [V]&lt;/strong&gt;다. 17,000 [V] 는 등급 1의 직류값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;내전압용 절연장갑의 등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;교류 (실효값)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;직류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색상&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;00&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;750 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;갈색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;0&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,500 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;빨간색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;1&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7,500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;11,250 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;흰색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;2&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;17,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25,500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;노란색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;3&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;26,500 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;39,750 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;녹색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;4&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;36,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;54,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;등색&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>등급 2의 직류 최대사용전압은 &lt;strong&gt;25,500 [V]&lt;/strong&gt;다. 17,000 [V]는 등급 1의 직류값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;내전압용 절연장갑의 등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;교류 (실효값)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;직류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색상&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;00&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;750 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;갈색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;0&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,500 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;빨간색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;1&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7,500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;11,250 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;흰색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;2&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;17,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25,500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;노란색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;3&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;26,500 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;39,750 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;녹색&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;4&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;36,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;54,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;등색&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 등급 00 의 교류 500 [V] 는 맞다.&lt;br&gt;② 등급 1 의 교류 7,500 [V] 는 맞다.&lt;br&gt;④ 등급 3 의 직류 39,750 [V] 는 맞다.</t>
+          <t>① 등급 00의 교류 500 [V]는 맞다.&lt;br&gt;② 등급 1의 교류 7,500 [V]는 맞다.&lt;br&gt;④ 등급 3의 직류 39,750 [V]는 맞다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내전압용 절연장갑의 등급별 최대사용전압&lt;/strong&gt;&lt;br&gt;직류값은 교류값의 &lt;strong&gt;1.5배&lt;/strong&gt;다. 교류값만 외우면 직류는 곱해서 구할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직류 = 교류 × 1.5&lt;/u&gt;. 등급 2 는 17,000 → 25,500.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;내전압용 절연장갑의 등급별 최대사용전압&lt;/strong&gt;&lt;br&gt;직류값은 교류값의 &lt;strong&gt;1.5배&lt;/strong&gt;다. 교류값만 외우면 직류는 곱해서 구할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직류 = 교류 × 1.5&lt;/u&gt;. 등급 2는 17,000 → 25,500.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10191,17 +10211,17 @@
       </c>
       <c r="AG71" s="32" t="inlineStr">
         <is>
-          <t>0종 장소에는 &lt;strong&gt;본질안전 방폭구조 ia&lt;/strong&gt;만 쓸 수 있다. &lt;strong&gt;2중 고장까지&lt;/strong&gt; 점화되지 않음을 보장하기 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험장소별로 쓸 수 있는 방폭구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스가 있는 정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;쓸 수 있는 구조&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;계속 또는 장시간 존재&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia 뿐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상 운전 중 때때로 생김&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ia · ib · d · p · o · e · m · q&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이상 시에만 잠깐&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;위의 것 모두 + &lt;u&gt;n&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>0종 장소에는 &lt;strong&gt;본질안전 방폭구조 ia&lt;/strong&gt;만 쓸 수 있다. &lt;strong&gt;2중 고장까지&lt;/strong&gt; 점화되지 않음을 보장하기 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험장소별로 쓸 수 있는 방폭구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스가 있는 정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;쓸 수 있는 구조&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;계속 또는 장시간 존재&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia뿐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상 운전 중 때때로 생김&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ia · ib · d · p · o · e · m · q&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이상 시에만 잠깐&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;위의 것 모두 + &lt;u&gt;n&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH71" s="32" t="inlineStr">
         <is>
-          <t>② ib 는 1중 고장까지만 보장하므로 1종 장소부터 쓴다.&lt;br&gt;③ Ex d(내압)는 1종 장소부터 쓴다.&lt;br&gt;④ Ex e(안전증)도 1종 장소부터 쓴다.</t>
+          <t>② ib는 1중 고장까지만 보장하므로 1종 장소부터 쓴다.&lt;br&gt;③ Ex d(내압)는 1종 장소부터 쓴다.&lt;br&gt;④ Ex e(안전증)도 1종 장소부터 쓴다.</t>
         </is>
       </c>
       <c r="AI71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험장소의 구분과 방폭구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;ia 는 2중 고장까지, ib 는 1중 고장까지&lt;/strong&gt; 안전을 보장한다. 이 한 줄이 문제 대부분을 가른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0종은 ia 뿐&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험장소의 구분과 방폭구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;ia는 2중 고장까지, ib는 1중 고장까지&lt;/strong&gt; 안전을 보장한다. 이 한 줄이 문제 대부분을 가른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0종은 ia뿐&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10325,7 +10345,7 @@
       </c>
       <c r="AH72" s="32" t="inlineStr">
         <is>
-          <t>① IP55 는 방진·방수 등급이 모두 낮다.&lt;br&gt;② IP56 은 방진 등급이 모자란다.&lt;br&gt;③ IP65 는 방수 등급이 모자란다.</t>
+          <t>① IP55는 방진·방수 등급이 모두 낮다.&lt;br&gt;② IP56은 방진 등급이 모자란다.&lt;br&gt;③ IP65는 방수 등급이 모자란다.</t>
         </is>
       </c>
       <c r="AI72" s="32" t="inlineStr">
@@ -10418,7 +10438,11 @@
           <t>KS C IEC 60079-0에 따른 방폭기기에 대한 설명이다. 다음 빈칸에 들어갈 알맞은 용어는?</t>
         </is>
       </c>
-      <c r="V73" s="32" t="inlineStr"/>
+      <c r="V73" s="32" t="inlineStr">
+        <is>
+          <t>( ⓐ )은 EPL로 표현되며 점화원이 될 수 있는 가능성에 기초하여 기기에 부여된 보호등급이다. EPL의 등급 중 ( ⓑ )는 정상 작동, 예상된 오작동, 드문 오작동 중에 점화원이 될 수 없는 「매우 높은」 보호 등급의 기기이다.</t>
+        </is>
+      </c>
       <c r="W73" s="32" t="inlineStr"/>
       <c r="X73" s="32" t="inlineStr">
         <is>
@@ -10449,17 +10473,17 @@
       </c>
       <c r="AG73" s="32" t="inlineStr">
         <is>
-          <t>EPL 은 &lt;strong&gt;Equipment Protection Level(기기보호등급)&lt;/strong&gt;의 줄임말이다. 「Explosion」이 아니다. 폭발성 가스 분위기에서 보호등급이 가장 높은 것이 &lt;strong&gt;EPL Ga&lt;/strong&gt;다.</t>
+          <t>EPL은 &lt;strong&gt;Equipment Protection Level(기기보호등급)&lt;/strong&gt;의 줄임말이다. 「Explosion」이 아니다. 폭발성 가스 분위기에서 보호등급이 가장 높은 것이 &lt;strong&gt;EPL Ga&lt;/strong&gt;다.</t>
         </is>
       </c>
       <c r="AH73" s="32" t="inlineStr">
         <is>
-          <t>① EPL 은 Explosion 이 아니라 Equipment 다.&lt;br&gt;② 앞뒤 모두 어긋난다.&lt;br&gt;④ Gc 는 「강화된」 보호등급으로 가장 낮은 쪽이다.</t>
+          <t>① EPL은 Explosion이 아니라 Equipment다.&lt;br&gt;② 앞뒤 모두 어긋난다.&lt;br&gt;④ Gc는 「강화된」 보호등급으로 가장 낮은 쪽이다.</t>
         </is>
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;기기보호등급(EPL)&lt;/strong&gt;&lt;br&gt;앞 글자는 대상 분위기 — &lt;strong&gt;G(가스) · D(분진) · M(광산)&lt;/strong&gt;. 뒤 글자는 보호 수준 — &lt;strong&gt;a(가장 높음) · b(높음) · c(강화된)&lt;/strong&gt;. &lt;strong&gt;M 에는 c 가 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;EPL 은 Equipment&lt;/u&gt; — Ga 가 가장 높다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;기기보호등급(EPL)&lt;/strong&gt;&lt;br&gt;앞 글자는 대상 분위기 — &lt;strong&gt;G(가스) · D(분진) · M(광산)&lt;/strong&gt;. 뒤 글자는 보호 수준 — &lt;strong&gt;a(가장 높음) · b(높음) · c(강화된)&lt;/strong&gt;. &lt;strong&gt;M 에는 c가 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;EPL은 Equipment&lt;/u&gt; — Ga가 가장 높다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10578,17 +10602,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$Q = C V = 10 \times 10^{-12} \times 5 \times 10^{3} = 5 \times 10^{-8}$ [C] 다.</t>
+          <t>$Q = C V = 10 \times 10^{-12} \times 5 \times 10^{3} = 5 \times 10^{-8}$ [C]다.</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① $9 \times 10^{-12}$ 은 전압을 곱하지 않은 값에 가깝다.&lt;br&gt;② $6 \times 10^{-10}$ 은 자릿수가 어긋난다.&lt;br&gt;④ $2 \times 10^{-6}$ 도 자릿수가 어긋난다.</t>
+          <t>① $9 \times 10^{-12}$은 전압을 곱하지 않은 값에 가깝다.&lt;br&gt;② $6 \times 10^{-10}$은 자릿수가 어긋난다.&lt;br&gt;④ $2 \times 10^{-6}$도 자릿수가 어긋난다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기의 전하량과 에너지&lt;/strong&gt;&lt;br&gt;세 관계식 — $Q = CV$&lt;strong&gt; · &lt;/strong&gt;$W = \dfrac{1}{2} C V^{2}$&lt;strong&gt; · &lt;/strong&gt;$V = Q / C$. 최소발화에너지와 견주어 폭발 위험을 판단할 때 두 번째 식을 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Q = CV$ — pF 는 $10^{-12}$, kV 는 $10^{3}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기의 전하량과 에너지&lt;/strong&gt;&lt;br&gt;세 관계식 — $Q = CV$&lt;strong&gt; · &lt;/strong&gt;$W = \dfrac{1}{2} C V^{2}$&lt;strong&gt; · &lt;/strong&gt;$V = Q / C$. 최소발화에너지와 견주어 폭발 위험을 판단할 때 두 번째 식을 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Q = CV$ — pF는 $10^{-12}$, kV는 $10^{3}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10712,12 +10736,12 @@
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① OS(유입 개폐기)는 기름 속에서 개폐한다.&lt;br&gt;② VCB 는 진공에서 아크를 끄는 고압용이다.&lt;br&gt;④ ACB 는 대기 중에서 아크를 끄는 저압 대용량이다.</t>
+          <t>① OS(유입 개폐기)는 기름 속에서 개폐한다.&lt;br&gt;② VCB는 진공에서 아크를 끄는 고압용이다.&lt;br&gt;④ ACB는 대기 중에서 아크를 끄는 저압 대용량이다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;차단기의 종류와 소호 방식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;MCCB 는 과부하와 단락&lt;/strong&gt;, &lt;strong&gt;ELB(누전차단기)는 누전&lt;/strong&gt;을 맡는다. 역할이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;몰드 케이스면 MCCB&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;차단기의 종류와 소호 방식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;MCCB는 과부하와 단락&lt;/strong&gt;, &lt;strong&gt;ELB(누전차단기)는 누전&lt;/strong&gt;을 맡는다. 역할이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;몰드 케이스면 MCCB&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10836,17 +10860,17 @@
       </c>
       <c r="AG76" s="32" t="inlineStr">
         <is>
-          <t>ⅡA 의 대표 가스는 &lt;strong&gt;프로판&lt;/strong&gt;이다. &lt;strong&gt;에틸렌은 ⅡB&lt;/strong&gt;, &lt;strong&gt;수소·아세틸렌은 ⅡC&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;기기그룹과 대표 가스&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;그룹&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대표 가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최대안전틈새&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소점화전류비&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;프로판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.9 [mm] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.8 초과&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.5~0.9 [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.45~0.8&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 · 아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.5 [mm] 미만&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.45 미만&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>ⅡA의 대표 가스는 &lt;strong&gt;프로판&lt;/strong&gt;이다. &lt;strong&gt;에틸렌은 ⅡB&lt;/strong&gt;, &lt;strong&gt;수소·아세틸렌은 ⅡC&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;기기그룹과 대표 가스&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;그룹&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대표 가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최대안전틈새&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소점화전류비&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;프로판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.9 [mm] 초과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.8 초과&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.5~0.9 [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.45~0.8&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소 · 아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.5 [mm] 미만&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.45 미만&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH76" s="32" t="inlineStr">
         <is>
-          <t>① 접미사 X 는 특정사용조건이 있음을 나타낸다.&lt;br&gt;② 폭발범위가 넓을수록 폭발성 분위기가 만들어지기 쉽다.&lt;br&gt;④ 연면거리는 고체 절연물 표면을 따른 최단거리가 맞다.</t>
+          <t>① 접미사 X는 특정사용조건이 있음을 나타낸다.&lt;br&gt;② 폭발범위가 넓을수록 폭발성 분위기가 만들어지기 쉽다.&lt;br&gt;④ 연면거리는 고체 절연물 표면을 따른 최단거리가 맞다.</t>
         </is>
       </c>
       <c r="AI76" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;KS C IEC 60079-0 — 기기그룹의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;C 로 갈수록 위험&lt;/strong&gt; 하다. 틈새가 좁고 적은 전류로도 불이 붙기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡA 프로판 · ⅡB 에틸렌 · ⅡC 수소·아세틸렌&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;KS C IEC 60079-0 — 기기그룹의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;C로 갈수록 위험&lt;/strong&gt;하다. 틈새가 좁고 적은 전류로도 불이 붙기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡA 프로판 · ⅡB 에틸렌 · ⅡC 수소·아세틸렌&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11069,7 @@
         <v>1</v>
       </c>
       <c r="Q78" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R78" s="32" t="inlineStr">
         <is>
@@ -11055,7 +11079,7 @@
       <c r="S78" s="32" t="inlineStr"/>
       <c r="T78" s="32" t="inlineStr">
         <is>
-          <t>원본 시행일 2022.04.24 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도1</t>
+          <t>원본 시행일 2022.04.24 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2</t>
         </is>
       </c>
       <c r="U78" s="32" t="inlineStr">
@@ -11063,7 +11087,11 @@
           <t>다음 설명이 나타내는 현상은?</t>
         </is>
       </c>
-      <c r="V78" s="32" t="inlineStr"/>
+      <c r="V78" s="32" t="inlineStr">
+        <is>
+          <t>전압이 인가된 이극 도체간의 고체 절연물 표면에 이물질이 부착되면 미소방전이 일어난다. 이 미소방전이 반복되면서 절연물 표면에 도전성 통로가 형성되는 현상이다.</t>
+        </is>
+      </c>
       <c r="W78" s="32" t="inlineStr"/>
       <c r="X78" s="32" t="inlineStr">
         <is>
@@ -11223,12 +11251,12 @@
       </c>
       <c r="AG79" s="32" t="inlineStr">
         <is>
-          <t>누설전류는 최대공급전류의 &lt;strong&gt;1/2,000 이하&lt;/strong&gt; 여야 한다. $I = 20 {,} 000 / ( \sqrt{3} \times 220 ) = 52.5$ [A] 이고 상전류 기준으로 $I_{g} = 52.5 / 2 {,} 000 = 0.02625$ [A] 다. $R = 220 / \sqrt{3} / 0.02625 \fallingdotseq 8 {,} 383$ [Ω] 이다.</t>
+          <t>누설전류는 최대공급전류의 &lt;strong&gt;1/2,000 이하&lt;/strong&gt; 여야 한다. $I = 20 {,} 000 / ( \sqrt{3} \times 220 ) = 52.5$ [A]이고 상전류 기준으로 $I_{g} = 52.5 / 2 {,} 000 = 0.02625$ [A]다. $R = 220 / \sqrt{3} / 0.02625 \fallingdotseq 8 {,} 383$ [Ω]이다.</t>
         </is>
       </c>
       <c r="AH79" s="32" t="inlineStr">
         <is>
-          <t>① 1240 은 자릿수가 크게 어긋난다.&lt;br&gt;② 2794 는 누설 기준을 1/1,000 으로 잡았을 때 쪽에 가깝다.&lt;br&gt;③ 4840 은 선간전압을 그대로 썼을 때 나온다.</t>
+          <t>① 1240은 자릿수가 크게 어긋난다.&lt;br&gt;② 2794는 누설 기준을 1/1,000으로 잡았을 때 쪽에 가깝다.&lt;br&gt;③ 4840은 선간전압을 그대로 썼을 때 나온다.</t>
         </is>
       </c>
       <c r="AI79" s="32" t="inlineStr">
@@ -11620,7 +11648,7 @@
       </c>
       <c r="AI82" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제전기의 제전효율&lt;/strong&gt;&lt;br&gt;제전기는 &lt;strong&gt;공기를 이온화&lt;/strong&gt; 해 반대 극성 이온으로 전하를 중화한다. 종류는 &lt;strong&gt;전압인가식 · 자기방전식 · 방사선식&lt;/strong&gt;이며, &lt;strong&gt;부도체에도 통한다&lt;/strong&gt;는 것이 큰 장점이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제전효율 90 [%] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;제전기의 제전효율&lt;/strong&gt;&lt;br&gt;제전기는 &lt;strong&gt;공기를 이온화&lt;/strong&gt;해 반대 극성 이온으로 전하를 중화한다. 종류는 &lt;strong&gt;전압인가식 · 자기방전식 · 방사선식&lt;/strong&gt;이며, &lt;strong&gt;부도체에도 통한다&lt;/strong&gt;는 것이 큰 장점이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제전효율 90 [%] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11739,17 +11767,17 @@
       </c>
       <c r="AG83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;에틸렌&lt;/strong&gt;이 약 0.07 [mJ] 로 가장 작다. 최소발화에너지가 작다는 것은 &lt;strong&gt;아주 작은 불꽃에도 불이 붙는다&lt;/strong&gt;는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 최소발화에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;MIE&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.009 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 작다 — 유속 1 [m/s] 이하로 제한&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 · 아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.019 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ⅡC 그룹&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.07 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ⅡB 그룹 — 에틸렌이 대표&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;에탄&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.25 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;메탄&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.28 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;아세트알데히드&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.36 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;에틸렌&lt;/strong&gt;이 약 0.07 [mJ]로 가장 작다. 최소발화에너지가 작다는 것은 &lt;strong&gt;아주 작은 불꽃에도 불이 붙는다&lt;/strong&gt;는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 최소발화에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;MIE&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.009 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 작다 — 유속 1 [m/s] 이하로 제한&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 · 아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.019 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ⅡC 그룹&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.07 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ⅡB 그룹 — 에틸렌이 대표&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;에탄&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.25 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;메탄&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.28 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;아세트알데히드&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.36 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH83" s="32" t="inlineStr">
         <is>
-          <t>② 아세트알데히드는 약 0.36 [mJ] 다.&lt;br&gt;③ 메탄은 약 0.28 [mJ] 다.&lt;br&gt;④ 에탄은 약 0.25 [mJ] 다.</t>
+          <t>② 아세트알데히드는 약 0.36 [mJ]다.&lt;br&gt;③ 메탄은 약 0.28 [mJ]다.&lt;br&gt;④ 에탄은 약 0.25 [mJ]다.</t>
         </is>
       </c>
       <c r="AI83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소발화에너지(MIE)&lt;/strong&gt;&lt;br&gt;MIE 는 &lt;strong&gt;온도·압력·산소농도가 높을수록 작아지고&lt;/strong&gt;, 화학양론 농도 부근에서 가장 작다. 사람이 느끼는 정전기 방전이 1~10 [mJ] 이므로, 이 값들은 &lt;strong&gt;느끼지도 못하는 방전으로 불이 붙는&lt;/strong&gt; 수준이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작을수록 위험&lt;/u&gt; — 이황화탄소 0.009 &amp;lt; 수소 0.019 &amp;lt; 에틸렌 0.07.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소발화에너지(MIE)&lt;/strong&gt;&lt;br&gt;MIE는 &lt;strong&gt;온도·압력·산소농도가 높을수록 작아지고&lt;/strong&gt;, 화학양론 농도 부근에서 가장 작다. 사람이 느끼는 정전기 방전이 1~10 [mJ]이므로, 이 값들은 &lt;strong&gt;느끼지도 못하는 방전으로 불이 붙는&lt;/strong&gt; 수준이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작을수록 위험&lt;/u&gt; — 이황화탄소 0.009 &amp;lt; 수소 0.019 &amp;lt; 에틸렌 0.07.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11868,7 +11896,7 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인화칼슘(Ca₃P₂)&lt;/strong&gt;이다. $\mathrm{Ca}_{3} P_{2} + 6 H_{2} O \rightarrow 3 \mathrm{Ca} ( OH )_{2} + 2 PH_{3}$ 로 &lt;strong&gt;포스핀(PH₃)&lt;/strong&gt;이 나온다. 맹독성이면서 자연발화성도 있다.</t>
+          <t>&lt;strong&gt;인화칼슘(Ca₃P₂)&lt;/strong&gt;이다. $\mathrm{Ca}_{3} P_{2} + 6 H_{2} O \rightarrow 3 \mathrm{Ca} ( OH )_{2} + 2 PH_{3}$로 &lt;strong&gt;포스핀(PH₃)&lt;/strong&gt;이 나온다. 맹독성이면서 자연발화성도 있다.</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
@@ -11997,7 +12025,7 @@
       </c>
       <c r="AG85" s="32" t="inlineStr">
         <is>
-          <t>에틸알코올은 $C_{2} H_{5} OH$ 다. $C_{2} H_{5} OH + 3 O_{2} \rightarrow 2 CO_{2} + 3 H_{2} O$ 이므로 &lt;strong&gt;CO₂ 2몰, H₂O 3몰&lt;/strong&gt;이다. &lt;strong&gt;탄소 수만큼 CO₂, 수소 수의 절반만큼 H₂O&lt;/strong&gt;가 나온다.</t>
+          <t>에틸알코올은 $C_{2} H_{5} OH$다. $C_{2} H_{5} OH + 3 O_{2} \rightarrow 2 CO_{2} + 3 H_{2} O$이므로 &lt;strong&gt;CO₂ 2몰, H₂O 3몰&lt;/strong&gt;이다. &lt;strong&gt;탄소 수만큼 CO₂, 수소 수의 절반만큼 H₂O&lt;/strong&gt;가 나온다.</t>
         </is>
       </c>
       <c r="AH85" s="32" t="inlineStr">
@@ -12007,7 +12035,7 @@
       </c>
       <c r="AI85" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;완전연소 반응식의 계수 맞추기&lt;/strong&gt;&lt;br&gt;$C_{n} H_{m} O_{l}$ 의 완전연소는 $C_{n} H_{m} O_{l} + ( n + \dfrac{m}{4} - \dfrac{l}{2} ) O_{2} \rightarrow \text{n CO}_{2} + \dfrac{m}{2} H_{2} O$ 다. 이 식을 알면 완전연소 조성농도 $C_{\mathrm{st}}$ 도 바로 구할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CO₂ 는 탄소 수, H₂O 는 수소 수의 절반&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;완전연소 반응식의 계수 맞추기&lt;/strong&gt;&lt;br&gt;$C_{n} H_{m} O_{l}$의 완전연소는 $C_{n} H_{m} O_{l} + ( n + \dfrac{m}{4} - \dfrac{l}{2} ) O_{2} \rightarrow \text{n CO}_{2} + \dfrac{m}{2} H_{2} O$다. 이 식을 알면 완전연소 조성농도 $C_{\mathrm{st}}$도 바로 구할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CO₂ 는 탄소 수, H₂O는 수소 수의 절반&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12252,11 @@
           <t>화염방지기의 설치에 관한 사항으로 ( )에 알맞은 것은?</t>
         </is>
       </c>
-      <c r="V87" s="32" t="inlineStr"/>
+      <c r="V87" s="32" t="inlineStr">
+        <is>
+          <t>사업주는 인화성 액체 및 인화성 가스를 저장·취급하는 화학설비에서 증기나 가스를 대기로 방출하는 경우에는 외부로부터의 화염을 방지하기 위하여 화염방지기를 그 설비 (      )에 설치하여야 한다.</t>
+        </is>
+      </c>
       <c r="W87" s="32" t="inlineStr"/>
       <c r="X87" s="32" t="inlineStr">
         <is>
@@ -12384,12 +12416,12 @@
       </c>
       <c r="AG88" s="32" t="inlineStr">
         <is>
-          <t>$H = \dfrac{U - L}{L} = \dfrac{9.5 - 2.2}{2.2} = \dfrac{7.3}{2.2} \fallingdotseq 3.32$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 가스의 위험도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;폭발범위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험도 H&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2.5 ~ 81 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31.4&lt;/u&gt; — 가장 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4 ~ 75 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;17.8&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;이황화탄소&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1.2 ~ 44 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;35.7&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;프로판&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2.1 ~ 9.5 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3.5&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5 ~ 15 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0&lt;/u&gt; — 작다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$H = \dfrac{U - L}{L} = \dfrac{9.5 - 2.2}{2.2} = \dfrac{7.3}{2.2} \fallingdotseq 3.32$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 가스의 위험도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;폭발범위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험도 H&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2.5 ~ 81 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31.4&lt;/u&gt; — 가장 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4 ~ 75 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;17.8&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;이황화탄소&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1.2 ~ 44 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;35.7&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;프로판&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2.1 ~ 9.5 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3.5&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5 ~ 15 [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0&lt;/u&gt; — 작다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH88" s="32" t="inlineStr">
         <is>
-          <t>① 2.52 는 분모를 상한으로 잡았을 때 쪽이다.&lt;br&gt;③ 4.91 은 계산과 맞지 않는다.&lt;br&gt;④ 5.64 도 맞지 않는다.</t>
+          <t>① 2.52는 분모를 상한으로 잡았을 때 쪽이다.&lt;br&gt;③ 4.91은 계산과 맞지 않는다.&lt;br&gt;④ 5.64 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI88" s="32" t="inlineStr">
@@ -13029,12 +13061,12 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>크롬은 &lt;strong&gt;은백색 광택이 있는 금속&lt;/strong&gt;이다. 비중은 약 7.2 로 물보다 무겁고, 인체에 가장 해로운 것은 &lt;strong&gt;6가 크롬&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 중금속과 대표 질병&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;금속&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대표 질병&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수은&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미나마타병&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중추신경 장해&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카드뮴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이타이이타이병&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;신장 장해 · 골연화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크롬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비중격 천공 · 폐암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6가 크롬이 발암성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;납&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;납중독 (빈혈 · 신경 장해)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조혈 기능 장해&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;망간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;파킨슨 유사 증상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중추신경 장해&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>크롬은 &lt;strong&gt;은백색 광택이 있는 금속&lt;/strong&gt;이다. 비중은 약 7.2로 물보다 무겁고, 인체에 가장 해로운 것은 &lt;strong&gt;6가 크롬&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 중금속과 대표 질병&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;금속&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대표 질병&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수은&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미나마타병&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중추신경 장해&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;카드뮴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이타이이타이병&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;신장 장해 · 골연화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크롬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비중격 천공 · 폐암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6가 크롬이 발암성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;납&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;납중독 (빈혈 · 신경 장해)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조혈 기능 장해&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;망간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;파킨슨 유사 증상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중추신경 장해&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>② 미나마타병은 수은 중독으로 생긴다.&lt;br&gt;③ 크롬의 비중은 약 7.2 로 물보다 크다.&lt;br&gt;④ 가장 유해한 것은 3가가 아니라 6가 크롬이다.</t>
+          <t>② 미나마타병은 수은 중독으로 생긴다.&lt;br&gt;③ 크롬의 비중은 약 7.2로 물보다 크다.&lt;br&gt;④ 가장 유해한 것은 3가가 아니라 6가 크롬이다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
@@ -13163,7 +13195,7 @@
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>① CO 의 허용농도는 30 [ppm] 이다.&lt;br&gt;③ NH₃ 는 25 [ppm] 이다.&lt;br&gt;④ H₂ 는 독성가스가 아니라 폭발성 가스다.</t>
+          <t>① CO의 허용농도는 30 [ppm]이다.&lt;br&gt;③ NH₃ 는 25 [ppm]이다.&lt;br&gt;④ H₂ 는 독성가스가 아니라 폭발성 가스다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
@@ -13426,7 +13458,7 @@
       </c>
       <c r="AI96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제261조 — 안전밸브의 검사주기&lt;/strong&gt;&lt;br&gt;검사 뒤에는 &lt;strong&gt;납으로 봉인&lt;/strong&gt; 해 임의로 조정하지 못하게 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직접 접촉 1년 · 파열판 있으면 2년 · 우수 사업장 4년&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C261%EC%A1%B0" target="_blank"&gt;제261조(안전밸브 등의 설치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 다음 각 호의 어느 하나에 해당하는 설비에 대해서는 과압에 따른 폭발을 방지하기 위하여 폭발 방지 성능과 규격을 갖춘 안전밸브 또는 파열판(이하 "안전밸브등"이라 한다)을 설치하여야 한다. 다만, 안전밸브등에 상응하는 방호장치를 설치한 경우에는 그러하지 아니하다. &amp;lt;개정 2024.6.28&amp;gt;&lt;br&gt; 1. 압력용기(안지름이 150밀리미터 이하인 압력용기는 제외하며, 압력 용기 중 관형 열교환기의 경우에는 관의 파열로 인하여 상승한 압력이 압력용기의 최고사용압력을 초과할 우려가 있는 경우만 해당한다)&lt;br&gt; 2. 정변위 압축기&lt;br&gt; 3. 정변위 펌프(토출측에 차단밸브가 설치된 것만 해당한다)&lt;br&gt; 4. 배관(2개 이상의 밸브에 의하여 차단되어 대기온도에서 액체의 열팽창에 의하여 파열될 우려가 있는 것으로 한정한다)&lt;br&gt; 5. 그 밖의 화학설비 및 그 부속설비로서 해당 설비의 최고사용압력을 초과할 우려가 있는 것&lt;br&gt;② 제1항에 따라 안전밸브등을 설치하는 경우에는 다단형 압축기 또는 직렬로 접속된 공기압축기에 대해서는 각 단 또는 각 공기압축기별로 안전밸브등을 설치하여야 한다.&lt;br&gt;▶ ③ 제1항에 따라 설치된 안전밸브에 대해서는 다음 각 호의 구분에 따른 검사주기마다 국가교정기관에서 교정을 받은 압력계를 이용하여 설정압력에서 안전밸브가 적정하게 작동하는지를 검사한 후 &lt;strong&gt;납으로 봉인&lt;/strong&gt;하여 사용하여야 한다. 다만, 공기나 질소취급용기 등에 설치된 안전밸브 중 안전밸브 자체에 부착된 레버 또는 고리를 통하여 수시로 안전밸브가 적정하게 작동하는지를 확인할 수 있는 경우에는 검사하지 아니할 수 있고 &lt;strong&gt;납으로 봉인&lt;/strong&gt;하지 아니할 수 있다. &amp;lt;개정 2019.12.26, 2024.6.28&amp;gt;&lt;br&gt; 1. 화학공정 유체와 안전밸브의 디스크 또는 시트가 직접 접촉될 수 있도록 설치된 경우: 2년마다 1회 이상&lt;br&gt; 2. 안전밸브 전단에 파열판이 설치된 경우: 3년마다 1회 이상&lt;br&gt; 3. 영 제43조에 따른 공정안전보고서 제출 대상으로서 고용노동부장관이 실시하는 공정안전보고서 이행상태 평가결과가 우수한 사업장의 안전밸브의 경우: 4년마다 1회 이상&lt;br&gt;④ 제3항 각 호에 따른 검사주기에도 불구하고 안전밸브가 설치된 압력용기에 대하여 「고압가스 안전관리법」 제17조제2항에 따라 시장ㆍ군수 또는 구청장의 재검사를 받는 경우로서 압력용기의 재검사주기에 대하여 같은 법 시행규칙 별표22 제2호에 따라 산업통상부장관이 정하여 고시하는 기법에 따라 산정하여 그 적합성을 인정받은 경우에는 해당 안전밸브의 검사주기는 그 압력용기의 재검사주기에 따른다. &amp;lt;신설 2014.9.30, 2025.10.1&amp;gt;&lt;br&gt;▶ ⑤ 사업주는 제3항에 따라 &lt;strong&gt;납으로 봉인&lt;/strong&gt;된 안전밸브를 해체하거나 조정할 수 없도록 조치하여야 한다. &amp;lt;개정 2014.9.30&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제261조 — 안전밸브의 검사주기&lt;/strong&gt;&lt;br&gt;검사 뒤에는 &lt;strong&gt;납으로 봉인&lt;/strong&gt;해 임의로 조정하지 못하게 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직접 접촉 1년 · 파열판 있으면 2년 · 우수 사업장 4년&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C261%EC%A1%B0" target="_blank"&gt;제261조(안전밸브 등의 설치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 다음 각 호의 어느 하나에 해당하는 설비에 대해서는 과압에 따른 폭발을 방지하기 위하여 폭발 방지 성능과 규격을 갖춘 안전밸브 또는 파열판(이하 "안전밸브등"이라 한다)을 설치하여야 한다. 다만, 안전밸브등에 상응하는 방호장치를 설치한 경우에는 그러하지 아니하다. &amp;lt;개정 2024.6.28&amp;gt;&lt;br&gt; 1. 압력용기(안지름이 150밀리미터 이하인 압력용기는 제외하며, 압력 용기 중 관형 열교환기의 경우에는 관의 파열로 인하여 상승한 압력이 압력용기의 최고사용압력을 초과할 우려가 있는 경우만 해당한다)&lt;br&gt; 2. 정변위 압축기&lt;br&gt; 3. 정변위 펌프(토출측에 차단밸브가 설치된 것만 해당한다)&lt;br&gt; 4. 배관(2개 이상의 밸브에 의하여 차단되어 대기온도에서 액체의 열팽창에 의하여 파열될 우려가 있는 것으로 한정한다)&lt;br&gt; 5. 그 밖의 화학설비 및 그 부속설비로서 해당 설비의 최고사용압력을 초과할 우려가 있는 것&lt;br&gt;② 제1항에 따라 안전밸브등을 설치하는 경우에는 다단형 압축기 또는 직렬로 접속된 공기압축기에 대해서는 각 단 또는 각 공기압축기별로 안전밸브등을 설치하여야 한다.&lt;br&gt;▶ ③ 제1항에 따라 설치된 안전밸브에 대해서는 다음 각 호의 구분에 따른 검사주기마다 국가교정기관에서 교정을 받은 압력계를 이용하여 설정압력에서 안전밸브가 적정하게 작동하는지를 검사한 후 &lt;strong&gt;납으로 봉인&lt;/strong&gt;하여 사용하여야 한다. 다만, 공기나 질소취급용기 등에 설치된 안전밸브 중 안전밸브 자체에 부착된 레버 또는 고리를 통하여 수시로 안전밸브가 적정하게 작동하는지를 확인할 수 있는 경우에는 검사하지 아니할 수 있고 &lt;strong&gt;납으로 봉인&lt;/strong&gt;하지 아니할 수 있다. &amp;lt;개정 2019.12.26, 2024.6.28&amp;gt;&lt;br&gt; 1. 화학공정 유체와 안전밸브의 디스크 또는 시트가 직접 접촉될 수 있도록 설치된 경우: 2년마다 1회 이상&lt;br&gt; 2. 안전밸브 전단에 파열판이 설치된 경우: 3년마다 1회 이상&lt;br&gt; 3. 영 제43조에 따른 공정안전보고서 제출 대상으로서 고용노동부장관이 실시하는 공정안전보고서 이행상태 평가결과가 우수한 사업장의 안전밸브의 경우: 4년마다 1회 이상&lt;br&gt;④ 제3항 각 호에 따른 검사주기에도 불구하고 안전밸브가 설치된 압력용기에 대하여 「고압가스 안전관리법」 제17조제2항에 따라 시장ㆍ군수 또는 구청장의 재검사를 받는 경우로서 압력용기의 재검사주기에 대하여 같은 법 시행규칙 별표22 제2호에 따라 산업통상부장관이 정하여 고시하는 기법에 따라 산정하여 그 적합성을 인정받은 경우에는 해당 안전밸브의 검사주기는 그 압력용기의 재검사주기에 따른다. &amp;lt;신설 2014.9.30, 2025.10.1&amp;gt;&lt;br&gt;▶ ⑤ 사업주는 제3항에 따라 &lt;strong&gt;납으로 봉인&lt;/strong&gt;된 안전밸브를 해체하거나 조정할 수 없도록 조치하여야 한다. &amp;lt;개정 2014.9.30&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -13545,17 +13577,17 @@
       </c>
       <c r="AG97" s="32" t="inlineStr">
         <is>
-          <t>$Q = k A \dfrac{\Delta T}{L} = 0.037 \times 1 \times \dfrac{20}{0.2} = 3.7$ [kcal/h] 다.</t>
+          <t>$Q = k A \dfrac{\Delta T}{L} = 0.037 \times 1 \times \dfrac{20}{0.2} = 3.7$ [kcal/h]다.</t>
         </is>
       </c>
       <c r="AH97" s="32" t="inlineStr">
         <is>
-          <t>① 0.0037 은 두께로 나누지 않고 곱했을 때 나온다.&lt;br&gt;② 0.037 은 열전도율 값 자체다.&lt;br&gt;③ 1.37 은 계산과 맞지 않는다.</t>
+          <t>① 0.0037은 두께로 나누지 않고 곱했을 때 나온다.&lt;br&gt;② 0.037은 열전도율 값 자체다.&lt;br&gt;③ 1.37은 계산과 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI97" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;푸리에의 열전도 법칙&lt;/strong&gt;&lt;br&gt;$Q = k A \Delta T / L$. &lt;strong&gt;열전도율과 온도차에 비례하고 두께에 반비례&lt;/strong&gt; 한다. 반비례라 두께를 두 배로 해도 손실은 절반까지만 줄어든다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;두께로 나눈다&lt;/u&gt; — 곱하면 자릿수가 어긋난다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;푸리에의 열전도 법칙&lt;/strong&gt;&lt;br&gt;$Q = k A \Delta T / L$. &lt;strong&gt;열전도율과 온도차에 비례하고 두께에 반비례&lt;/strong&gt;한다. 반비례라 두께를 두 배로 해도 손실은 절반까지만 줄어든다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;두께로 나눈다&lt;/u&gt; — 곱하면 자릿수가 어긋난다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13964,7 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>$\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$ 로 &lt;strong&gt;수산화칼슘과 아세틸렌&lt;/strong&gt;이 나온다. 아세틸렌은 폭발범위가 &lt;strong&gt;2.5~81 [%]&lt;/strong&gt;로 대단히 넓어 곧바로 폭발로 이어진다.</t>
+          <t>$\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow \mathrm{Ca} ( OH )_{2} + C_{2} H_{2}$로 &lt;strong&gt;수산화칼슘과 아세틸렌&lt;/strong&gt;이 나온다. 아세틸렌은 폭발범위가 &lt;strong&gt;2.5~81 [%]&lt;/strong&gt;로 대단히 넓어 곧바로 폭발로 이어진다.</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
@@ -14071,7 +14103,7 @@
       </c>
       <c r="AI101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자연발화성 물질&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt; 일 때 일어난다. 발열의 종류로 갈리면 &lt;strong&gt;산화열(건성유·석탄) · 분해열(질화면) · 미생물열(퇴비) · 흡착열(활성탄) · 중합열(단량체)&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산화성 물질은 남을 태우지 스스로 타지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자연발화성 물질&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt;일 때 일어난다. 발열의 종류로 갈리면 &lt;strong&gt;산화열(건성유·석탄) · 분해열(질화면) · 미생물열(퇴비) · 흡착열(활성탄) · 중합열(단량체)&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산화성 물질은 남을 태우지 스스로 타지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14190,7 +14222,7 @@
       </c>
       <c r="AG102" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;이황화탄소는 오히려 물속에 저장&lt;/strong&gt; 한다. 물보다 무겁고 물에 녹지 않아 물이 위를 덮으면 증발이 막힌다. 인화점이 −30 [℃] 로 매우 낮아 증기를 막는 것이 관건이다.</t>
+          <t>&lt;strong&gt;이황화탄소는 오히려 물속에 저장&lt;/strong&gt;한다. 물보다 무겁고 물에 녹지 않아 물이 위를 덮으면 증발이 막힌다. 인화점이 −30 [℃]로 매우 낮아 증기를 막는 것이 관건이다.</t>
         </is>
       </c>
       <c r="AH102" s="32" t="inlineStr">
@@ -14329,7 +14361,7 @@
       </c>
       <c r="AI103" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;흙막이 계측기기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;무엇을 재는가&lt;/strong&gt;로 짝지으면 그대로 답이 된다. 하중계는 힘, 변형률계는 변형, 경사계는 기울기다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;load cell 은 하중, strain gauge 는 변형&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;흙막이 계측기기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;무엇을 재는가&lt;/strong&gt;로 짝지으면 그대로 답이 된다. 하중계는 힘, 변형률계는 변형, 경사계는 기울기다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;load cell은 하중, strain gauge는 변형&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14577,12 +14609,12 @@
       </c>
       <c r="AG105" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강관틀비계는 수직 6 [m], 수평 8 [m]&lt;/strong&gt;다. 단관비계의 5·5 와 헷갈리지 않아야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 조립간격 (별표5)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비계의 종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수직방향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수평방향&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단관비계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;틀비계&lt;/u&gt; (높이 5 [m] 미만 제외)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;강관틀비계는 수직 6 [m], 수평 8 [m]&lt;/strong&gt;다. 단관비계의 5·5와 헷갈리지 않아야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 조립간격 (별표5)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비계의 종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수직방향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수평방향&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단관비계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;틀비계&lt;/u&gt; (높이 5 [m] 미만 제외)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH105" s="32" t="inlineStr">
         <is>
-          <t>① 5 [m] · 5 [m] 는 단관비계의 기준이다.&lt;br&gt;② 수평 7 [m] 라는 기준은 없다.&lt;br&gt;④ 수직 7 [m] 라는 기준도 없다.</t>
+          <t>① 5 [m] · 5 [m]는 단관비계의 기준이다.&lt;br&gt;② 수평 7 [m]라는 기준은 없다.&lt;br&gt;④ 수직 7 [m]라는 기준도 없다.</t>
         </is>
       </c>
       <c r="AI105" s="32" t="inlineStr">
@@ -14840,7 +14872,7 @@
       </c>
       <c r="AH107" s="32" t="inlineStr">
         <is>
-          <t>② 6 [m] · 6 [m] 라는 기준은 없다.&lt;br&gt;③ 7 [m] · 7 [m] 도 없다.&lt;br&gt;④ 8 [m] 는 틀비계의 수평방향 값이다.</t>
+          <t>② 6 [m] · 6 [m]라는 기준은 없다.&lt;br&gt;③ 7 [m] · 7 [m] 도 없다.&lt;br&gt;④ 8 [m]는 틀비계의 수평방향 값이다.</t>
         </is>
       </c>
       <c r="AI107" s="32" t="inlineStr">
@@ -15614,7 +15646,7 @@
       </c>
       <c r="AH113" s="32" t="inlineStr">
         <is>
-          <t>① 40 [m] 는 기준에 미치지 못한다.&lt;br&gt;③ 60 [m] 라는 기준은 없다.&lt;br&gt;④ 70 [m] 라는 기준도 없다.</t>
+          <t>① 40 [m]는 기준에 미치지 못한다.&lt;br&gt;③ 60 [m]라는 기준은 없다.&lt;br&gt;④ 70 [m]라는 기준도 없다.</t>
         </is>
       </c>
       <c r="AI113" s="32" t="inlineStr">
@@ -15738,7 +15770,7 @@
       </c>
       <c r="AG114" s="32" t="inlineStr">
         <is>
-          <t>작업발판의 폭은 &lt;strong&gt;40 [cm] 이상&lt;/strong&gt;이다. 30 [cm] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업발판의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;작업발판의 폭&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;달비계는 20 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;발판재료 간 틈&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;달비계는 틈이 없도록&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;지지물 연결&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;뒤집힘 방지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;추락 위험 장소&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전난간 설치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>작업발판의 폭은 &lt;strong&gt;40 [cm] 이상&lt;/strong&gt;이다. 30 [cm]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업발판의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;작업발판의 폭&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;달비계는 20 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;발판재료 간 틈&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;달비계는 틈이 없도록&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;지지물 연결&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;뒤집힘 방지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;추락 위험 장소&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전난간 설치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH114" s="32" t="inlineStr">
@@ -15748,7 +15780,7 @@
       </c>
       <c r="AI114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제56조 — 작업발판의 구조&lt;/strong&gt;&lt;br&gt;사람이 두 발로 서서 몸을 돌릴 수 있어야 하므로 &lt;strong&gt;40 [cm]&lt;/strong&gt;이 나온다. 달비계는 매달린 구조라 예외로 20 [cm] 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;폭 40, 틈 3&lt;/u&gt; — 달비계만 20.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C56%EC%A1%B0" target="_blank"&gt;제56조(작업발판의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 비계(달비계, 달대비계 및 말비계는 제외한다)의 높이가 2미터 이상인 작업장소에 다음 각 호의 기준에 맞는 작업발판을 설치하여야 한다. &amp;lt;개정 2012.5.31, 2017.12.28&amp;gt;&lt;br&gt; 1. 발판재료는 작업할 때의 하중을 견딜 수 있도록 견고한 것으로 할 것&lt;br&gt;▶  2. &lt;strong&gt;작업발판의 폭은&lt;/strong&gt; 40센티미터 이상으로 하고, 발판재료 간의 틈은 3센티미터 이하로 할 것. 다만, 외줄비계의 경우에는 고용노동부장관이 별도로 정하는 기준에 따른다.&lt;br&gt; 3. 제2호에도 불구하고 선박 및 보트 건조작업의 경우 선박블록 또는 엔진실 등의 좁은 작업공간에 작업발판을 설치하기 위하여 필요하면 작업발판의 폭을 30센티미터 이상으로 할 수 있고, 걸침비계의 경우 강관기둥 때문에 발판재료 간의 틈을 3센티미터 이하로 유지하기 곤란하면 5센티미터 이하로 할 수 있다. 이 경우 그 틈 사이로 물체 등이 떨어질 우려가 있는 곳에는 출입금지 등의 조치를 하여야 한다.&lt;br&gt; 4. 추락의 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업의 성질상 안전난간을 설치하는 것이 곤란한 경우, 작업의 필요상 임시로 안전난간을 해체할 때에 추락방호망을 설치하거나 근로자로 하여금 안전대를 사용하도록 하는 등 추락위험 방지 조치를 한 경우에는 그러하지 아니하다.&lt;br&gt; 5. 작업발판의 지지물은 하중에 의하여 파괴될 우려가 없는 것을 사용할 것&lt;br&gt; 6. 작업발판재료는 뒤집히거나 떨어지지 않도록 둘 이상의 지지물에 연결하거나 고정시킬 것&lt;br&gt; 7. 작업발판을 작업에 따라 이동시킬 경우에는 위험 방지에 필요한 조치를 할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제56조 — 작업발판의 구조&lt;/strong&gt;&lt;br&gt;사람이 두 발로 서서 몸을 돌릴 수 있어야 하므로 &lt;strong&gt;40 [cm]&lt;/strong&gt;이 나온다. 달비계는 매달린 구조라 예외로 20 [cm]다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;폭 40, 틈 3&lt;/u&gt; — 달비계만 20.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C56%EC%A1%B0" target="_blank"&gt;제56조(작업발판의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 비계(달비계, 달대비계 및 말비계는 제외한다)의 높이가 2미터 이상인 작업장소에 다음 각 호의 기준에 맞는 작업발판을 설치하여야 한다. &amp;lt;개정 2012.5.31, 2017.12.28&amp;gt;&lt;br&gt; 1. 발판재료는 작업할 때의 하중을 견딜 수 있도록 견고한 것으로 할 것&lt;br&gt;▶  2. &lt;strong&gt;작업발판의 폭은&lt;/strong&gt; 40센티미터 이상으로 하고, 발판재료 간의 틈은 3센티미터 이하로 할 것. 다만, 외줄비계의 경우에는 고용노동부장관이 별도로 정하는 기준에 따른다.&lt;br&gt; 3. 제2호에도 불구하고 선박 및 보트 건조작업의 경우 선박블록 또는 엔진실 등의 좁은 작업공간에 작업발판을 설치하기 위하여 필요하면 작업발판의 폭을 30센티미터 이상으로 할 수 있고, 걸침비계의 경우 강관기둥 때문에 발판재료 간의 틈을 3센티미터 이하로 유지하기 곤란하면 5센티미터 이하로 할 수 있다. 이 경우 그 틈 사이로 물체 등이 떨어질 우려가 있는 곳에는 출입금지 등의 조치를 하여야 한다.&lt;br&gt; 4. 추락의 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업의 성질상 안전난간을 설치하는 것이 곤란한 경우, 작업의 필요상 임시로 안전난간을 해체할 때에 추락방호망을 설치하거나 근로자로 하여금 안전대를 사용하도록 하는 등 추락위험 방지 조치를 한 경우에는 그러하지 아니하다.&lt;br&gt; 5. 작업발판의 지지물은 하중에 의하여 파괴될 우려가 없는 것을 사용할 것&lt;br&gt; 6. 작업발판재료는 뒤집히거나 떨어지지 않도록 둘 이상의 지지물에 연결하거나 고정시킬 것&lt;br&gt; 7. 작업발판을 작업에 따라 이동시킬 경우에는 위험 방지에 필요한 조치를 할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -15867,7 +15899,7 @@
       </c>
       <c r="AG115" s="32" t="inlineStr">
         <is>
-          <t>사다리식 통로의 폭은 &lt;strong&gt;30 [cm] 이상&lt;/strong&gt;이다. 40 [cm] 는 &lt;strong&gt;작업발판&lt;/strong&gt;의 기준이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사다리식 통로의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;폭&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업발판 40 과 다르다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;발판과 벽 사이&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;발이 들어갈 틈&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;상단 돌출&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;붙잡을 곳&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;기울기&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고정식은 90° 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;길이 10 [m] 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 이내마다 계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>사다리식 통로의 폭은 &lt;strong&gt;30 [cm] 이상&lt;/strong&gt;이다. 40 [cm]는 &lt;strong&gt;작업발판&lt;/strong&gt;의 기준이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사다리식 통로의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;폭&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업발판 40과 다르다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;발판과 벽 사이&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;발이 들어갈 틈&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;상단 돌출&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;붙잡을 곳&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;기울기&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고정식은 90° 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;길이 10 [m] 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 이내마다 계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH115" s="32" t="inlineStr">
@@ -15996,7 +16028,7 @@
       </c>
       <c r="AG116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;수평연결재&lt;/strong&gt;는 동바리가 옆으로 휘는 &lt;strong&gt;좌굴&lt;/strong&gt;을 막는 것이지 &lt;strong&gt;침하&lt;/strong&gt;를 막는 것이 아니다. 침하는 &lt;strong&gt;발밑을 단단히&lt;/strong&gt; 해서 막는다.</t>
+          <t>&lt;strong&gt;수평연결재&lt;/strong&gt;는 동바리가 옆으로 휘는 &lt;strong&gt;좌굴&lt;/strong&gt;을 막는 것이지 &lt;strong&gt;침하&lt;/strong&gt;를 막는 것이 아니다. 침하는 &lt;strong&gt;발밑을 단단히&lt;/strong&gt;해서 막는다.</t>
         </is>
       </c>
       <c r="AH116" s="32" t="inlineStr">
@@ -16130,7 +16162,7 @@
       </c>
       <c r="AH117" s="32" t="inlineStr">
         <is>
-          <t>① 20 [cm] 는 기준보다 촘촘해 오르내리기 번거롭다.&lt;br&gt;② 25 [cm] 도 기준보다 촘촘하다.&lt;br&gt;④ 40 [cm] 는 발이 닿기 어려워 기준을 넘는다.</t>
+          <t>① 20 [cm]는 기준보다 촘촘해 오르내리기 번거롭다.&lt;br&gt;② 25 [cm] 도 기준보다 촘촘하다.&lt;br&gt;④ 40 [cm]는 발이 닿기 어려워 기준을 넘는다.</t>
         </is>
       </c>
       <c r="AI117" s="32" t="inlineStr">
@@ -16375,7 +16407,7 @@
       </c>
       <c r="AG119" s="32" t="inlineStr">
         <is>
-          <t>순서가 거꾸로다. &lt;strong&gt;연직부재(기둥·벽)를 먼저, 수평부재(보 밑·슬래브)를 나중에&lt;/strong&gt; 뗀다. 기둥과 벽은 제 무게만 견디면 되지만 보와 슬래브는 &lt;strong&gt;휨을 받아 하중을 계속 지탱&lt;/strong&gt; 해야 한다.&lt;img src="safe_A_2026_02_117_exp1.png"&gt;&lt;em&gt;거푸집 해체 순서 — 옆은 빨리, 밑은 늦게&lt;/em&gt;</t>
+          <t>순서가 거꾸로다. &lt;strong&gt;연직부재(기둥·벽)를 먼저, 수평부재(보 밑·슬래브)를 나중에&lt;/strong&gt; 뗀다. 기둥과 벽은 제 무게만 견디면 되지만 보와 슬래브는 &lt;strong&gt;휨을 받아 하중을 계속 지탱&lt;/strong&gt;해야 한다.&lt;img src="safe_A_2026_02_117_exp1.png"&gt;&lt;em&gt;거푸집 해체 순서 — 옆은 빨리, 밑은 늦게&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH119" s="32" t="inlineStr">
@@ -16767,7 +16799,7 @@
       </c>
       <c r="AH122" s="32" t="inlineStr">
         <is>
-          <t>① Load Cell 은 버팀보·앵커의 축하중을 잰다.&lt;br&gt;② Inclinometer 는 흙의 수평변위(기울기)를 잰다.&lt;br&gt;③ Extensometer 는 지중 변위나 신장량을 잰다.</t>
+          <t>① Load Cell은 버팀보·앵커의 축하중을 잰다.&lt;br&gt;② Inclinometer는 흙의 수평변위(기울기)를 잰다.&lt;br&gt;③ Extensometer는 지중 변위나 신장량을 잰다.</t>
         </is>
       </c>
       <c r="AI122" s="32" t="inlineStr">
